--- a/1234567.xlxs.xlsx
+++ b/1234567.xlxs.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/BED19DC7E2258E89/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{889A1873-6274-420E-9E95-2BF90E81F51C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE56FED6-253D-4C47-80EF-48B39A0E1958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -120,6 +123,9 @@
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
   </si>
   <si>
+    <t>5. GOOD PRACTICE</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
@@ -132,13 +138,22 @@
     <t>Name:</t>
   </si>
   <si>
+    <t xml:space="preserve">Sachi Lakhanpal  </t>
+  </si>
+  <si>
     <t>Registration No.:</t>
   </si>
   <si>
     <t>Course / Section:</t>
   </si>
   <si>
+    <t>MCA /D1P2635</t>
+  </si>
+  <si>
     <t>Month:</t>
+  </si>
+  <si>
+    <t>August</t>
   </si>
   <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -186,25 +201,13 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Neutral</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>5. GOOD PRACTICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sachi Lakhanpal  </t>
-  </si>
-  <si>
-    <t>August</t>
-  </si>
-  <si>
-    <t>Neutral</t>
-  </si>
-  <si>
     <t xml:space="preserve">Felt a bit tired after my 9 to 5 classes. </t>
-  </si>
-  <si>
-    <t>MCA /D1P2635</t>
   </si>
   <si>
     <t>Good</t>
@@ -230,6 +233,9 @@
   <si>
     <t xml:space="preserve">Mood was good </t>
   </si>
+  <si>
+    <t>Mood is good feeling homesick</t>
+  </si>
 </sst>
 </file>
 
@@ -238,7 +244,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -408,9 +414,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,10 +513,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -693,186 +695,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" ht="23.1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="16.5">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1">
       <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1">
       <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1">
       <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1">
       <c r="A33" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
       <c r="A34" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
       <c r="A35" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
@@ -884,7 +886,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N401"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
@@ -897,121 +899,121 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-    </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A1" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+    </row>
+    <row r="2" spans="1:14" ht="19.5" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="19">
+        <v>12623846</v>
+      </c>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="1:14" ht="19.5" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="19"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+    </row>
+    <row r="5" spans="1:14" ht="42">
+      <c r="A5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="20">
-        <v>12623846</v>
-      </c>
-      <c r="G2" s="20"/>
-    </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="20" t="s">
+      <c r="N5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-    </row>
-    <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:14" ht="29.1">
       <c r="A6" s="8">
         <v>46252</v>
       </c>
@@ -1051,13 +1053,13 @@
         <v>53</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="13">
         <v>46253</v>
       </c>
@@ -1097,13 +1099,13 @@
         <v>57</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="N7" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="43.5">
       <c r="A8" s="13">
         <v>46254</v>
       </c>
@@ -1143,13 +1145,13 @@
         <v>53</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="N8" s="17" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9" s="13">
         <v>46255</v>
       </c>
@@ -1189,13 +1191,13 @@
         <v>57</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10" s="13">
         <v>46256</v>
       </c>
@@ -1241,51 +1243,99 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+    <row r="11" spans="1:14" ht="15">
+      <c r="A11" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B11" s="14">
+        <v>400</v>
+      </c>
+      <c r="C11" s="14">
+        <v>20</v>
+      </c>
+      <c r="D11" s="14">
+        <v>50</v>
+      </c>
+      <c r="E11" s="14">
+        <v>35</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>60</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>565</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+        <v>875</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15">
+      <c r="A12" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B12" s="14">
+        <v>360</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>60</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>150</v>
+      </c>
+      <c r="G12" s="14">
+        <v>3</v>
+      </c>
+      <c r="H12" s="14">
+        <v>20</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>650</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+        <v>790</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="13"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -1307,7 +1357,7 @@
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="A14" s="13"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -1329,7 +1379,7 @@
       <c r="M14" s="16"/>
       <c r="N14" s="17"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -1351,7 +1401,7 @@
       <c r="M15" s="16"/>
       <c r="N15" s="17"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="A16" s="13"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -1373,7 +1423,7 @@
       <c r="M16" s="16"/>
       <c r="N16" s="17"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17" s="13"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -1395,7 +1445,7 @@
       <c r="M17" s="16"/>
       <c r="N17" s="17"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18" s="13"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
@@ -1417,7 +1467,7 @@
       <c r="M18" s="16"/>
       <c r="N18" s="17"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19" s="13"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -1439,7 +1489,7 @@
       <c r="M19" s="16"/>
       <c r="N19" s="17"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14">
       <c r="A20" s="13"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -1461,7 +1511,7 @@
       <c r="M20" s="16"/>
       <c r="N20" s="17"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14">
       <c r="A21" s="13"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -1483,7 +1533,7 @@
       <c r="M21" s="16"/>
       <c r="N21" s="17"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14">
       <c r="A22" s="13"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -1505,7 +1555,7 @@
       <c r="M22" s="16"/>
       <c r="N22" s="17"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14">
       <c r="A23" s="13"/>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
@@ -1527,7 +1577,7 @@
       <c r="M23" s="16"/>
       <c r="N23" s="17"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14">
       <c r="A24" s="13"/>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -1549,7 +1599,7 @@
       <c r="M24" s="16"/>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14">
       <c r="A25" s="13"/>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -1571,7 +1621,7 @@
       <c r="M25" s="16"/>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14">
       <c r="A26" s="13"/>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -1593,7 +1643,7 @@
       <c r="M26" s="16"/>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14">
       <c r="A27" s="13"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -1615,7 +1665,7 @@
       <c r="M27" s="16"/>
       <c r="N27" s="17"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -1637,7 +1687,7 @@
       <c r="M28" s="16"/>
       <c r="N28" s="17"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14">
       <c r="A29" s="13"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -1659,7 +1709,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="17"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -1681,7 +1731,7 @@
       <c r="M30" s="16"/>
       <c r="N30" s="17"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14">
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -1703,7 +1753,7 @@
       <c r="M31" s="16"/>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14">
       <c r="A32" s="13"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -1725,7 +1775,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -1747,7 +1797,7 @@
       <c r="M33" s="16"/>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
@@ -1769,7 +1819,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -1791,7 +1841,7 @@
       <c r="M35" s="16"/>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -1813,7 +1863,7 @@
       <c r="M36" s="16"/>
       <c r="N36" s="17"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
@@ -1835,7 +1885,7 @@
       <c r="M37" s="16"/>
       <c r="N37" s="17"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -1857,7 +1907,7 @@
       <c r="M38" s="16"/>
       <c r="N38" s="17"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14">
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -1879,7 +1929,7 @@
       <c r="M39" s="16"/>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -1901,7 +1951,7 @@
       <c r="M40" s="16"/>
       <c r="N40" s="17"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14">
       <c r="A41" s="13"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
@@ -1923,7 +1973,7 @@
       <c r="M41" s="16"/>
       <c r="N41" s="17"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14">
       <c r="A42" s="13"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
@@ -1945,7 +1995,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14">
       <c r="A43" s="13"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -1967,7 +2017,7 @@
       <c r="M43" s="16"/>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -1989,7 +2039,7 @@
       <c r="M44" s="16"/>
       <c r="N44" s="17"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14">
       <c r="A45" s="13"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -2011,7 +2061,7 @@
       <c r="M45" s="16"/>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -2033,7 +2083,7 @@
       <c r="M46" s="16"/>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -2055,7 +2105,7 @@
       <c r="M47" s="16"/>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -2077,7 +2127,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -2099,7 +2149,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -2121,7 +2171,7 @@
       <c r="M50" s="16"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -2143,7 +2193,7 @@
       <c r="M51" s="16"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14">
       <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -2165,7 +2215,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14">
       <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -2187,7 +2237,7 @@
       <c r="M53" s="16"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -2209,7 +2259,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14">
       <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -2231,7 +2281,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -2253,7 +2303,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14">
       <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -2275,7 +2325,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14">
       <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -2297,7 +2347,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14">
       <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -2319,7 +2369,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="17"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14">
       <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -2341,7 +2391,7 @@
       <c r="M60" s="16"/>
       <c r="N60" s="17"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -2363,7 +2413,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="17"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14">
       <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -2385,7 +2435,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="17"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14">
       <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -2407,7 +2457,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="17"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14">
       <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -2429,7 +2479,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -2451,7 +2501,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="17"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14">
       <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -2473,7 +2523,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -2495,7 +2545,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="17"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14">
       <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -2517,7 +2567,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="17"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -2539,7 +2589,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -2561,7 +2611,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14">
       <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -2583,7 +2633,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="17"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -2605,7 +2655,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14">
       <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -2627,7 +2677,7 @@
       <c r="M73" s="16"/>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14">
       <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -2649,7 +2699,7 @@
       <c r="M74" s="16"/>
       <c r="N74" s="17"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -2671,7 +2721,7 @@
       <c r="M75" s="16"/>
       <c r="N75" s="17"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -2693,7 +2743,7 @@
       <c r="M76" s="16"/>
       <c r="N76" s="17"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14">
       <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -2715,7 +2765,7 @@
       <c r="M77" s="16"/>
       <c r="N77" s="17"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14">
       <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -2737,7 +2787,7 @@
       <c r="M78" s="16"/>
       <c r="N78" s="17"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14">
       <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -2759,7 +2809,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="17"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -2781,7 +2831,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="17"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14">
       <c r="A81" s="13"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
@@ -2803,7 +2853,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="17"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14">
       <c r="A82" s="13"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
@@ -2825,7 +2875,7 @@
       <c r="M82" s="16"/>
       <c r="N82" s="17"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14">
       <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
@@ -2847,7 +2897,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="17"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14">
       <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -2869,7 +2919,7 @@
       <c r="M84" s="16"/>
       <c r="N84" s="17"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14">
       <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
@@ -2891,7 +2941,7 @@
       <c r="M85" s="16"/>
       <c r="N85" s="17"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14">
       <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -2913,7 +2963,7 @@
       <c r="M86" s="16"/>
       <c r="N86" s="17"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14">
       <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -2935,7 +2985,7 @@
       <c r="M87" s="16"/>
       <c r="N87" s="17"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14">
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -2957,7 +3007,7 @@
       <c r="M88" s="16"/>
       <c r="N88" s="17"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14">
       <c r="A89" s="13"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
@@ -2979,7 +3029,7 @@
       <c r="M89" s="16"/>
       <c r="N89" s="17"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14">
       <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -3001,7 +3051,7 @@
       <c r="M90" s="16"/>
       <c r="N90" s="17"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14">
       <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
@@ -3023,7 +3073,7 @@
       <c r="M91" s="16"/>
       <c r="N91" s="17"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14">
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -3045,7 +3095,7 @@
       <c r="M92" s="16"/>
       <c r="N92" s="17"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14">
       <c r="A93" s="13"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -3067,7 +3117,7 @@
       <c r="M93" s="16"/>
       <c r="N93" s="17"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14">
       <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -3089,7 +3139,7 @@
       <c r="M94" s="16"/>
       <c r="N94" s="17"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14">
       <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -3111,7 +3161,7 @@
       <c r="M95" s="16"/>
       <c r="N95" s="17"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14">
       <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
@@ -3133,7 +3183,7 @@
       <c r="M96" s="16"/>
       <c r="N96" s="17"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:14">
       <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
@@ -3155,7 +3205,7 @@
       <c r="M97" s="16"/>
       <c r="N97" s="17"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14">
       <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -3177,7 +3227,7 @@
       <c r="M98" s="16"/>
       <c r="N98" s="17"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:14">
       <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
@@ -3199,7 +3249,7 @@
       <c r="M99" s="16"/>
       <c r="N99" s="17"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:14">
       <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
@@ -3221,7 +3271,7 @@
       <c r="M100" s="16"/>
       <c r="N100" s="17"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:14">
       <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
@@ -3243,7 +3293,7 @@
       <c r="M101" s="16"/>
       <c r="N101" s="17"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:14">
       <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
@@ -3265,7 +3315,7 @@
       <c r="M102" s="16"/>
       <c r="N102" s="17"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:14">
       <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
@@ -3287,7 +3337,7 @@
       <c r="M103" s="16"/>
       <c r="N103" s="17"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:14">
       <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -3309,7 +3359,7 @@
       <c r="M104" s="16"/>
       <c r="N104" s="17"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:14">
       <c r="A105" s="13"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
@@ -3331,7 +3381,7 @@
       <c r="M105" s="16"/>
       <c r="N105" s="17"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:14">
       <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
@@ -3353,7 +3403,7 @@
       <c r="M106" s="16"/>
       <c r="N106" s="17"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:14">
       <c r="A107" s="13"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
@@ -3375,7 +3425,7 @@
       <c r="M107" s="16"/>
       <c r="N107" s="17"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14">
       <c r="A108" s="13"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
@@ -3397,7 +3447,7 @@
       <c r="M108" s="16"/>
       <c r="N108" s="17"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14">
       <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
@@ -3419,7 +3469,7 @@
       <c r="M109" s="16"/>
       <c r="N109" s="17"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14">
       <c r="A110" s="13"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
@@ -3441,7 +3491,7 @@
       <c r="M110" s="16"/>
       <c r="N110" s="17"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14">
       <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
@@ -3463,7 +3513,7 @@
       <c r="M111" s="16"/>
       <c r="N111" s="17"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14">
       <c r="A112" s="13"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
@@ -3485,7 +3535,7 @@
       <c r="M112" s="16"/>
       <c r="N112" s="17"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14">
       <c r="A113" s="13"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
@@ -3507,7 +3557,7 @@
       <c r="M113" s="16"/>
       <c r="N113" s="17"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14">
       <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
@@ -3529,7 +3579,7 @@
       <c r="M114" s="16"/>
       <c r="N114" s="17"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14">
       <c r="A115" s="13"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
@@ -3551,7 +3601,7 @@
       <c r="M115" s="16"/>
       <c r="N115" s="17"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14">
       <c r="A116" s="13"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -3573,7 +3623,7 @@
       <c r="M116" s="16"/>
       <c r="N116" s="17"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14">
       <c r="A117" s="13"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
@@ -3595,7 +3645,7 @@
       <c r="M117" s="16"/>
       <c r="N117" s="17"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14">
       <c r="A118" s="13"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
@@ -3617,7 +3667,7 @@
       <c r="M118" s="16"/>
       <c r="N118" s="17"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14">
       <c r="A119" s="13"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
@@ -3639,7 +3689,7 @@
       <c r="M119" s="16"/>
       <c r="N119" s="17"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14">
       <c r="A120" s="13"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
@@ -3661,7 +3711,7 @@
       <c r="M120" s="16"/>
       <c r="N120" s="17"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14">
       <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
@@ -3683,7 +3733,7 @@
       <c r="M121" s="16"/>
       <c r="N121" s="17"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14">
       <c r="A122" s="13"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -3705,7 +3755,7 @@
       <c r="M122" s="16"/>
       <c r="N122" s="17"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14">
       <c r="A123" s="13"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -3727,7 +3777,7 @@
       <c r="M123" s="16"/>
       <c r="N123" s="17"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14">
       <c r="A124" s="13"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
@@ -3749,7 +3799,7 @@
       <c r="M124" s="16"/>
       <c r="N124" s="17"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14">
       <c r="A125" s="13"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
@@ -3771,7 +3821,7 @@
       <c r="M125" s="16"/>
       <c r="N125" s="17"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14">
       <c r="A126" s="13"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
@@ -3793,7 +3843,7 @@
       <c r="M126" s="16"/>
       <c r="N126" s="17"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14">
       <c r="A127" s="13"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -3815,7 +3865,7 @@
       <c r="M127" s="16"/>
       <c r="N127" s="17"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14">
       <c r="A128" s="13"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -3837,7 +3887,7 @@
       <c r="M128" s="16"/>
       <c r="N128" s="17"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14">
       <c r="A129" s="13"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
@@ -3859,7 +3909,7 @@
       <c r="M129" s="16"/>
       <c r="N129" s="17"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:14">
       <c r="A130" s="13"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
@@ -3881,7 +3931,7 @@
       <c r="M130" s="16"/>
       <c r="N130" s="17"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:14">
       <c r="A131" s="13"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
@@ -3903,7 +3953,7 @@
       <c r="M131" s="16"/>
       <c r="N131" s="17"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:14">
       <c r="A132" s="13"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
@@ -3925,7 +3975,7 @@
       <c r="M132" s="16"/>
       <c r="N132" s="17"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:14">
       <c r="A133" s="13"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
@@ -3947,7 +3997,7 @@
       <c r="M133" s="16"/>
       <c r="N133" s="17"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:14">
       <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -3969,7 +4019,7 @@
       <c r="M134" s="16"/>
       <c r="N134" s="17"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:14">
       <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
@@ -3991,7 +4041,7 @@
       <c r="M135" s="16"/>
       <c r="N135" s="17"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:14">
       <c r="A136" s="13"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
@@ -4013,7 +4063,7 @@
       <c r="M136" s="16"/>
       <c r="N136" s="17"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:14">
       <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
@@ -4035,7 +4085,7 @@
       <c r="M137" s="16"/>
       <c r="N137" s="17"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:14">
       <c r="A138" s="13"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
@@ -4057,7 +4107,7 @@
       <c r="M138" s="16"/>
       <c r="N138" s="17"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:14">
       <c r="A139" s="13"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
@@ -4079,7 +4129,7 @@
       <c r="M139" s="16"/>
       <c r="N139" s="17"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:14">
       <c r="A140" s="13"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
@@ -4101,7 +4151,7 @@
       <c r="M140" s="16"/>
       <c r="N140" s="17"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14">
       <c r="A141" s="13"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
@@ -4123,7 +4173,7 @@
       <c r="M141" s="16"/>
       <c r="N141" s="17"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:14">
       <c r="A142" s="13"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
@@ -4145,7 +4195,7 @@
       <c r="M142" s="16"/>
       <c r="N142" s="17"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14">
       <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
@@ -4167,7 +4217,7 @@
       <c r="M143" s="16"/>
       <c r="N143" s="17"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:14">
       <c r="A144" s="13"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
@@ -4189,7 +4239,7 @@
       <c r="M144" s="16"/>
       <c r="N144" s="17"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14">
       <c r="A145" s="13"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
@@ -4211,7 +4261,7 @@
       <c r="M145" s="16"/>
       <c r="N145" s="17"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:14">
       <c r="A146" s="13"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
@@ -4233,7 +4283,7 @@
       <c r="M146" s="16"/>
       <c r="N146" s="17"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:14">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
@@ -4255,7 +4305,7 @@
       <c r="M147" s="16"/>
       <c r="N147" s="17"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:14">
       <c r="A148" s="13"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
@@ -4277,7 +4327,7 @@
       <c r="M148" s="16"/>
       <c r="N148" s="17"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:14">
       <c r="A149" s="13"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
@@ -4299,7 +4349,7 @@
       <c r="M149" s="16"/>
       <c r="N149" s="17"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:14">
       <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
@@ -4321,7 +4371,7 @@
       <c r="M150" s="16"/>
       <c r="N150" s="17"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:14">
       <c r="A151" s="13"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
@@ -4343,7 +4393,7 @@
       <c r="M151" s="16"/>
       <c r="N151" s="17"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:14">
       <c r="A152" s="13"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
@@ -4365,7 +4415,7 @@
       <c r="M152" s="16"/>
       <c r="N152" s="17"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:14">
       <c r="A153" s="13"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
@@ -4387,7 +4437,7 @@
       <c r="M153" s="16"/>
       <c r="N153" s="17"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:14">
       <c r="A154" s="13"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
@@ -4409,7 +4459,7 @@
       <c r="M154" s="16"/>
       <c r="N154" s="17"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:14">
       <c r="A155" s="13"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
@@ -4431,7 +4481,7 @@
       <c r="M155" s="16"/>
       <c r="N155" s="17"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:14">
       <c r="A156" s="13"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
@@ -4453,7 +4503,7 @@
       <c r="M156" s="16"/>
       <c r="N156" s="17"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:14">
       <c r="A157" s="13"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
@@ -4475,7 +4525,7 @@
       <c r="M157" s="16"/>
       <c r="N157" s="17"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:14">
       <c r="A158" s="13"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
@@ -4497,7 +4547,7 @@
       <c r="M158" s="16"/>
       <c r="N158" s="17"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:14">
       <c r="A159" s="13"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
@@ -4519,7 +4569,7 @@
       <c r="M159" s="16"/>
       <c r="N159" s="17"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:14">
       <c r="A160" s="13"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
@@ -4541,7 +4591,7 @@
       <c r="M160" s="16"/>
       <c r="N160" s="17"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:14">
       <c r="A161" s="13"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
@@ -4563,7 +4613,7 @@
       <c r="M161" s="16"/>
       <c r="N161" s="17"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:14">
       <c r="A162" s="13"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
@@ -4585,7 +4635,7 @@
       <c r="M162" s="16"/>
       <c r="N162" s="17"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:14">
       <c r="A163" s="13"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
@@ -4607,7 +4657,7 @@
       <c r="M163" s="16"/>
       <c r="N163" s="17"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:14">
       <c r="A164" s="13"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
@@ -4629,7 +4679,7 @@
       <c r="M164" s="16"/>
       <c r="N164" s="17"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:14">
       <c r="A165" s="13"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
@@ -4651,7 +4701,7 @@
       <c r="M165" s="16"/>
       <c r="N165" s="17"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:14">
       <c r="A166" s="13"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
@@ -4673,7 +4723,7 @@
       <c r="M166" s="16"/>
       <c r="N166" s="17"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:14">
       <c r="A167" s="13"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
@@ -4695,7 +4745,7 @@
       <c r="M167" s="16"/>
       <c r="N167" s="17"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:14">
       <c r="A168" s="13"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
@@ -4717,7 +4767,7 @@
       <c r="M168" s="16"/>
       <c r="N168" s="17"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:14">
       <c r="A169" s="13"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
@@ -4739,7 +4789,7 @@
       <c r="M169" s="16"/>
       <c r="N169" s="17"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:14">
       <c r="A170" s="13"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
@@ -4761,7 +4811,7 @@
       <c r="M170" s="16"/>
       <c r="N170" s="17"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:14">
       <c r="A171" s="13"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
@@ -4783,7 +4833,7 @@
       <c r="M171" s="16"/>
       <c r="N171" s="17"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:14">
       <c r="A172" s="13"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
@@ -4805,7 +4855,7 @@
       <c r="M172" s="16"/>
       <c r="N172" s="17"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:14">
       <c r="A173" s="13"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
@@ -4827,7 +4877,7 @@
       <c r="M173" s="16"/>
       <c r="N173" s="17"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:14">
       <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
@@ -4849,7 +4899,7 @@
       <c r="M174" s="16"/>
       <c r="N174" s="17"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:14">
       <c r="A175" s="13"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
@@ -4871,7 +4921,7 @@
       <c r="M175" s="16"/>
       <c r="N175" s="17"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:14">
       <c r="A176" s="13"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
@@ -4893,7 +4943,7 @@
       <c r="M176" s="16"/>
       <c r="N176" s="17"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:14">
       <c r="A177" s="13"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
@@ -4915,7 +4965,7 @@
       <c r="M177" s="16"/>
       <c r="N177" s="17"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:14">
       <c r="A178" s="13"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
@@ -4937,7 +4987,7 @@
       <c r="M178" s="16"/>
       <c r="N178" s="17"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:14">
       <c r="A179" s="13"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
@@ -4959,7 +5009,7 @@
       <c r="M179" s="16"/>
       <c r="N179" s="17"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:14">
       <c r="A180" s="13"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
@@ -4981,7 +5031,7 @@
       <c r="M180" s="16"/>
       <c r="N180" s="17"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:14">
       <c r="A181" s="13"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
@@ -5003,7 +5053,7 @@
       <c r="M181" s="16"/>
       <c r="N181" s="17"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:14">
       <c r="A182" s="13"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -5025,7 +5075,7 @@
       <c r="M182" s="16"/>
       <c r="N182" s="17"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:14">
       <c r="A183" s="13"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
@@ -5047,7 +5097,7 @@
       <c r="M183" s="16"/>
       <c r="N183" s="17"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:14">
       <c r="A184" s="13"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
@@ -5069,7 +5119,7 @@
       <c r="M184" s="16"/>
       <c r="N184" s="17"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:14">
       <c r="A185" s="13"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
@@ -5091,7 +5141,7 @@
       <c r="M185" s="16"/>
       <c r="N185" s="17"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:14">
       <c r="A186" s="13"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -5113,7 +5163,7 @@
       <c r="M186" s="16"/>
       <c r="N186" s="17"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:14">
       <c r="A187" s="13"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
@@ -5135,7 +5185,7 @@
       <c r="M187" s="16"/>
       <c r="N187" s="17"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:14">
       <c r="A188" s="13"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
@@ -5157,7 +5207,7 @@
       <c r="M188" s="16"/>
       <c r="N188" s="17"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:14">
       <c r="A189" s="13"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
@@ -5179,7 +5229,7 @@
       <c r="M189" s="16"/>
       <c r="N189" s="17"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:14">
       <c r="A190" s="13"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
@@ -5201,7 +5251,7 @@
       <c r="M190" s="16"/>
       <c r="N190" s="17"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:14">
       <c r="A191" s="13"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
@@ -5223,7 +5273,7 @@
       <c r="M191" s="16"/>
       <c r="N191" s="17"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:14">
       <c r="A192" s="13"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -5245,7 +5295,7 @@
       <c r="M192" s="16"/>
       <c r="N192" s="17"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:14">
       <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -5267,7 +5317,7 @@
       <c r="M193" s="16"/>
       <c r="N193" s="17"/>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:14">
       <c r="A194" s="13"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -5289,7 +5339,7 @@
       <c r="M194" s="16"/>
       <c r="N194" s="17"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:14">
       <c r="A195" s="13"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
@@ -5311,7 +5361,7 @@
       <c r="M195" s="16"/>
       <c r="N195" s="17"/>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:14">
       <c r="A196" s="13"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
@@ -5333,7 +5383,7 @@
       <c r="M196" s="16"/>
       <c r="N196" s="17"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:14">
       <c r="A197" s="13"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
@@ -5355,7 +5405,7 @@
       <c r="M197" s="16"/>
       <c r="N197" s="17"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:14">
       <c r="A198" s="13"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
@@ -5377,7 +5427,7 @@
       <c r="M198" s="16"/>
       <c r="N198" s="17"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:14">
       <c r="A199" s="13"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
@@ -5399,7 +5449,7 @@
       <c r="M199" s="16"/>
       <c r="N199" s="17"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:14">
       <c r="A200" s="13"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
@@ -5421,7 +5471,7 @@
       <c r="M200" s="16"/>
       <c r="N200" s="17"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:14">
       <c r="A201" s="13"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
@@ -5443,7 +5493,7 @@
       <c r="M201" s="16"/>
       <c r="N201" s="17"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:14">
       <c r="A202" s="13"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -5465,7 +5515,7 @@
       <c r="M202" s="16"/>
       <c r="N202" s="17"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:14">
       <c r="A203" s="13"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
@@ -5487,7 +5537,7 @@
       <c r="M203" s="16"/>
       <c r="N203" s="17"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:14">
       <c r="A204" s="13"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
@@ -5509,7 +5559,7 @@
       <c r="M204" s="16"/>
       <c r="N204" s="17"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:14">
       <c r="A205" s="13"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
@@ -5531,7 +5581,7 @@
       <c r="M205" s="16"/>
       <c r="N205" s="17"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:14">
       <c r="A206" s="13"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
@@ -5553,7 +5603,7 @@
       <c r="M206" s="16"/>
       <c r="N206" s="17"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:14">
       <c r="A207" s="13"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
@@ -5575,7 +5625,7 @@
       <c r="M207" s="16"/>
       <c r="N207" s="17"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:14">
       <c r="A208" s="13"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
@@ -5597,7 +5647,7 @@
       <c r="M208" s="16"/>
       <c r="N208" s="17"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:14">
       <c r="A209" s="13"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
@@ -5619,7 +5669,7 @@
       <c r="M209" s="16"/>
       <c r="N209" s="17"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:14">
       <c r="A210" s="13"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
@@ -5641,7 +5691,7 @@
       <c r="M210" s="16"/>
       <c r="N210" s="17"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:14">
       <c r="A211" s="13"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
@@ -5663,7 +5713,7 @@
       <c r="M211" s="16"/>
       <c r="N211" s="17"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:14">
       <c r="A212" s="13"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
@@ -5685,7 +5735,7 @@
       <c r="M212" s="16"/>
       <c r="N212" s="17"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:14">
       <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
@@ -5707,7 +5757,7 @@
       <c r="M213" s="16"/>
       <c r="N213" s="17"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:14">
       <c r="A214" s="13"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
@@ -5729,7 +5779,7 @@
       <c r="M214" s="16"/>
       <c r="N214" s="17"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:14">
       <c r="A215" s="13"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
@@ -5751,7 +5801,7 @@
       <c r="M215" s="16"/>
       <c r="N215" s="17"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:14">
       <c r="A216" s="13"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
@@ -5773,7 +5823,7 @@
       <c r="M216" s="16"/>
       <c r="N216" s="17"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:14">
       <c r="A217" s="13"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
@@ -5795,7 +5845,7 @@
       <c r="M217" s="16"/>
       <c r="N217" s="17"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:14">
       <c r="A218" s="13"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
@@ -5817,7 +5867,7 @@
       <c r="M218" s="16"/>
       <c r="N218" s="17"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:14">
       <c r="A219" s="13"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
@@ -5839,7 +5889,7 @@
       <c r="M219" s="16"/>
       <c r="N219" s="17"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:14">
       <c r="A220" s="13"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
@@ -5861,7 +5911,7 @@
       <c r="M220" s="16"/>
       <c r="N220" s="17"/>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:14">
       <c r="A221" s="13"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
@@ -5883,7 +5933,7 @@
       <c r="M221" s="16"/>
       <c r="N221" s="17"/>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:14">
       <c r="A222" s="13"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
@@ -5905,7 +5955,7 @@
       <c r="M222" s="16"/>
       <c r="N222" s="17"/>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:14">
       <c r="A223" s="13"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
@@ -5927,7 +5977,7 @@
       <c r="M223" s="16"/>
       <c r="N223" s="17"/>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:14">
       <c r="A224" s="13"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
@@ -5949,7 +5999,7 @@
       <c r="M224" s="16"/>
       <c r="N224" s="17"/>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:14">
       <c r="A225" s="13"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
@@ -5971,7 +6021,7 @@
       <c r="M225" s="16"/>
       <c r="N225" s="17"/>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:14">
       <c r="A226" s="13"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
@@ -5993,7 +6043,7 @@
       <c r="M226" s="16"/>
       <c r="N226" s="17"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:14">
       <c r="A227" s="13"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
@@ -6015,7 +6065,7 @@
       <c r="M227" s="16"/>
       <c r="N227" s="17"/>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:14">
       <c r="A228" s="13"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
@@ -6037,7 +6087,7 @@
       <c r="M228" s="16"/>
       <c r="N228" s="17"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:14">
       <c r="A229" s="13"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
@@ -6059,7 +6109,7 @@
       <c r="M229" s="16"/>
       <c r="N229" s="17"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:14">
       <c r="A230" s="13"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
@@ -6081,7 +6131,7 @@
       <c r="M230" s="16"/>
       <c r="N230" s="17"/>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:14">
       <c r="A231" s="13"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
@@ -6103,7 +6153,7 @@
       <c r="M231" s="16"/>
       <c r="N231" s="17"/>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:14">
       <c r="A232" s="13"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
@@ -6125,7 +6175,7 @@
       <c r="M232" s="16"/>
       <c r="N232" s="17"/>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:14">
       <c r="A233" s="13"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
@@ -6147,7 +6197,7 @@
       <c r="M233" s="16"/>
       <c r="N233" s="17"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:14">
       <c r="A234" s="13"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
@@ -6169,7 +6219,7 @@
       <c r="M234" s="16"/>
       <c r="N234" s="17"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:14">
       <c r="A235" s="13"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
@@ -6191,7 +6241,7 @@
       <c r="M235" s="16"/>
       <c r="N235" s="17"/>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:14">
       <c r="A236" s="13"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
@@ -6213,7 +6263,7 @@
       <c r="M236" s="16"/>
       <c r="N236" s="17"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:14">
       <c r="A237" s="13"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
@@ -6235,7 +6285,7 @@
       <c r="M237" s="16"/>
       <c r="N237" s="17"/>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:14">
       <c r="A238" s="13"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
@@ -6257,7 +6307,7 @@
       <c r="M238" s="16"/>
       <c r="N238" s="17"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:14">
       <c r="A239" s="13"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
@@ -6279,7 +6329,7 @@
       <c r="M239" s="16"/>
       <c r="N239" s="17"/>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:14">
       <c r="A240" s="13"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
@@ -6301,7 +6351,7 @@
       <c r="M240" s="16"/>
       <c r="N240" s="17"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:14">
       <c r="A241" s="13"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
@@ -6323,7 +6373,7 @@
       <c r="M241" s="16"/>
       <c r="N241" s="17"/>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:14">
       <c r="A242" s="13"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
@@ -6345,7 +6395,7 @@
       <c r="M242" s="16"/>
       <c r="N242" s="17"/>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:14">
       <c r="A243" s="13"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
@@ -6367,7 +6417,7 @@
       <c r="M243" s="16"/>
       <c r="N243" s="17"/>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:14">
       <c r="A244" s="13"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
@@ -6389,7 +6439,7 @@
       <c r="M244" s="16"/>
       <c r="N244" s="17"/>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:14">
       <c r="A245" s="13"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
@@ -6411,7 +6461,7 @@
       <c r="M245" s="16"/>
       <c r="N245" s="17"/>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:14">
       <c r="A246" s="13"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
@@ -6433,7 +6483,7 @@
       <c r="M246" s="16"/>
       <c r="N246" s="17"/>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:14">
       <c r="A247" s="13"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
@@ -6455,7 +6505,7 @@
       <c r="M247" s="16"/>
       <c r="N247" s="17"/>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:14">
       <c r="A248" s="13"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
@@ -6477,7 +6527,7 @@
       <c r="M248" s="16"/>
       <c r="N248" s="17"/>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:14">
       <c r="A249" s="13"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
@@ -6499,7 +6549,7 @@
       <c r="M249" s="16"/>
       <c r="N249" s="17"/>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:14">
       <c r="A250" s="13"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
@@ -6521,7 +6571,7 @@
       <c r="M250" s="16"/>
       <c r="N250" s="17"/>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:14">
       <c r="A251" s="13"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
@@ -6543,7 +6593,7 @@
       <c r="M251" s="16"/>
       <c r="N251" s="17"/>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:14">
       <c r="A252" s="13"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
@@ -6565,7 +6615,7 @@
       <c r="M252" s="16"/>
       <c r="N252" s="17"/>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:14">
       <c r="A253" s="13"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
@@ -6587,7 +6637,7 @@
       <c r="M253" s="16"/>
       <c r="N253" s="17"/>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:14">
       <c r="A254" s="13"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
@@ -6609,7 +6659,7 @@
       <c r="M254" s="16"/>
       <c r="N254" s="17"/>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:14">
       <c r="A255" s="13"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
@@ -6631,7 +6681,7 @@
       <c r="M255" s="16"/>
       <c r="N255" s="17"/>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:14">
       <c r="A256" s="13"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
@@ -6653,7 +6703,7 @@
       <c r="M256" s="16"/>
       <c r="N256" s="17"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:14">
       <c r="A257" s="13"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
@@ -6675,7 +6725,7 @@
       <c r="M257" s="16"/>
       <c r="N257" s="17"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:14">
       <c r="A258" s="13"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
@@ -6697,7 +6747,7 @@
       <c r="M258" s="16"/>
       <c r="N258" s="17"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:14">
       <c r="A259" s="13"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
@@ -6719,7 +6769,7 @@
       <c r="M259" s="16"/>
       <c r="N259" s="17"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:14">
       <c r="A260" s="13"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
@@ -6741,7 +6791,7 @@
       <c r="M260" s="16"/>
       <c r="N260" s="17"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:14">
       <c r="A261" s="13"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
@@ -6763,7 +6813,7 @@
       <c r="M261" s="16"/>
       <c r="N261" s="17"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:14">
       <c r="A262" s="13"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
@@ -6785,7 +6835,7 @@
       <c r="M262" s="16"/>
       <c r="N262" s="17"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:14">
       <c r="A263" s="13"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
@@ -6807,7 +6857,7 @@
       <c r="M263" s="16"/>
       <c r="N263" s="17"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:14">
       <c r="A264" s="13"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
@@ -6829,7 +6879,7 @@
       <c r="M264" s="16"/>
       <c r="N264" s="17"/>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:14">
       <c r="A265" s="13"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
@@ -6851,7 +6901,7 @@
       <c r="M265" s="16"/>
       <c r="N265" s="17"/>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:14">
       <c r="A266" s="13"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
@@ -6873,7 +6923,7 @@
       <c r="M266" s="16"/>
       <c r="N266" s="17"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:14">
       <c r="A267" s="13"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
@@ -6895,7 +6945,7 @@
       <c r="M267" s="16"/>
       <c r="N267" s="17"/>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:14">
       <c r="A268" s="13"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
@@ -6917,7 +6967,7 @@
       <c r="M268" s="16"/>
       <c r="N268" s="17"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:14">
       <c r="A269" s="13"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
@@ -6939,7 +6989,7 @@
       <c r="M269" s="16"/>
       <c r="N269" s="17"/>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:14">
       <c r="A270" s="13"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
@@ -6961,7 +7011,7 @@
       <c r="M270" s="16"/>
       <c r="N270" s="17"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:14">
       <c r="A271" s="13"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
@@ -6983,7 +7033,7 @@
       <c r="M271" s="16"/>
       <c r="N271" s="17"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:14">
       <c r="A272" s="13"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
@@ -7005,7 +7055,7 @@
       <c r="M272" s="16"/>
       <c r="N272" s="17"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:14">
       <c r="A273" s="13"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
@@ -7027,7 +7077,7 @@
       <c r="M273" s="16"/>
       <c r="N273" s="17"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:14">
       <c r="A274" s="13"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
@@ -7049,7 +7099,7 @@
       <c r="M274" s="16"/>
       <c r="N274" s="17"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:14">
       <c r="A275" s="13"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
@@ -7071,7 +7121,7 @@
       <c r="M275" s="16"/>
       <c r="N275" s="17"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:14">
       <c r="A276" s="13"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
@@ -7093,7 +7143,7 @@
       <c r="M276" s="16"/>
       <c r="N276" s="17"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:14">
       <c r="A277" s="13"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
@@ -7115,7 +7165,7 @@
       <c r="M277" s="16"/>
       <c r="N277" s="17"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:14">
       <c r="A278" s="13"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
@@ -7137,7 +7187,7 @@
       <c r="M278" s="16"/>
       <c r="N278" s="17"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:14">
       <c r="A279" s="13"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
@@ -7159,7 +7209,7 @@
       <c r="M279" s="16"/>
       <c r="N279" s="17"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:14">
       <c r="A280" s="13"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
@@ -7181,7 +7231,7 @@
       <c r="M280" s="16"/>
       <c r="N280" s="17"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:14">
       <c r="A281" s="13"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
@@ -7203,7 +7253,7 @@
       <c r="M281" s="16"/>
       <c r="N281" s="17"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:14">
       <c r="A282" s="13"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
@@ -7225,7 +7275,7 @@
       <c r="M282" s="16"/>
       <c r="N282" s="17"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:14">
       <c r="A283" s="13"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
@@ -7247,7 +7297,7 @@
       <c r="M283" s="16"/>
       <c r="N283" s="17"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:14">
       <c r="A284" s="13"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
@@ -7269,7 +7319,7 @@
       <c r="M284" s="16"/>
       <c r="N284" s="17"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:14">
       <c r="A285" s="13"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
@@ -7291,7 +7341,7 @@
       <c r="M285" s="16"/>
       <c r="N285" s="17"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:14">
       <c r="A286" s="13"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
@@ -7313,7 +7363,7 @@
       <c r="M286" s="16"/>
       <c r="N286" s="17"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:14">
       <c r="A287" s="13"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
@@ -7335,7 +7385,7 @@
       <c r="M287" s="16"/>
       <c r="N287" s="17"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:14">
       <c r="A288" s="13"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
@@ -7357,7 +7407,7 @@
       <c r="M288" s="16"/>
       <c r="N288" s="17"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:14">
       <c r="A289" s="13"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
@@ -7379,7 +7429,7 @@
       <c r="M289" s="16"/>
       <c r="N289" s="17"/>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:14">
       <c r="A290" s="13"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
@@ -7401,7 +7451,7 @@
       <c r="M290" s="16"/>
       <c r="N290" s="17"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:14">
       <c r="A291" s="13"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
@@ -7423,7 +7473,7 @@
       <c r="M291" s="16"/>
       <c r="N291" s="17"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:14">
       <c r="A292" s="13"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
@@ -7445,7 +7495,7 @@
       <c r="M292" s="16"/>
       <c r="N292" s="17"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:14">
       <c r="A293" s="13"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
@@ -7467,7 +7517,7 @@
       <c r="M293" s="16"/>
       <c r="N293" s="17"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:14">
       <c r="A294" s="13"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
@@ -7489,7 +7539,7 @@
       <c r="M294" s="16"/>
       <c r="N294" s="17"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:14">
       <c r="A295" s="13"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
@@ -7511,7 +7561,7 @@
       <c r="M295" s="16"/>
       <c r="N295" s="17"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:14">
       <c r="A296" s="13"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
@@ -7533,7 +7583,7 @@
       <c r="M296" s="16"/>
       <c r="N296" s="17"/>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:14">
       <c r="A297" s="13"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
@@ -7555,7 +7605,7 @@
       <c r="M297" s="16"/>
       <c r="N297" s="17"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:14">
       <c r="A298" s="13"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
@@ -7577,7 +7627,7 @@
       <c r="M298" s="16"/>
       <c r="N298" s="17"/>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:14">
       <c r="A299" s="13"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
@@ -7599,7 +7649,7 @@
       <c r="M299" s="16"/>
       <c r="N299" s="17"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:14">
       <c r="A300" s="13"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
@@ -7621,7 +7671,7 @@
       <c r="M300" s="16"/>
       <c r="N300" s="17"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:14">
       <c r="A301" s="13"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
@@ -7643,7 +7693,7 @@
       <c r="M301" s="16"/>
       <c r="N301" s="17"/>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:14">
       <c r="A302" s="13"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
@@ -7665,7 +7715,7 @@
       <c r="M302" s="16"/>
       <c r="N302" s="17"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:14">
       <c r="A303" s="13"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
@@ -7687,7 +7737,7 @@
       <c r="M303" s="16"/>
       <c r="N303" s="17"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:14">
       <c r="A304" s="13"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
@@ -7709,7 +7759,7 @@
       <c r="M304" s="16"/>
       <c r="N304" s="17"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:14">
       <c r="A305" s="13"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
@@ -7731,7 +7781,7 @@
       <c r="M305" s="16"/>
       <c r="N305" s="17"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:14">
       <c r="A306" s="13"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
@@ -7753,7 +7803,7 @@
       <c r="M306" s="16"/>
       <c r="N306" s="17"/>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:14">
       <c r="A307" s="13"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
@@ -7775,7 +7825,7 @@
       <c r="M307" s="16"/>
       <c r="N307" s="17"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:14">
       <c r="A308" s="13"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
@@ -7797,7 +7847,7 @@
       <c r="M308" s="16"/>
       <c r="N308" s="17"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:14">
       <c r="A309" s="13"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
@@ -7819,7 +7869,7 @@
       <c r="M309" s="16"/>
       <c r="N309" s="17"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:14">
       <c r="A310" s="13"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
@@ -7841,7 +7891,7 @@
       <c r="M310" s="16"/>
       <c r="N310" s="17"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:14">
       <c r="A311" s="13"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
@@ -7863,7 +7913,7 @@
       <c r="M311" s="16"/>
       <c r="N311" s="17"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:14">
       <c r="A312" s="13"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
@@ -7885,7 +7935,7 @@
       <c r="M312" s="16"/>
       <c r="N312" s="17"/>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:14">
       <c r="A313" s="13"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
@@ -7907,7 +7957,7 @@
       <c r="M313" s="16"/>
       <c r="N313" s="17"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:14">
       <c r="A314" s="13"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
@@ -7929,7 +7979,7 @@
       <c r="M314" s="16"/>
       <c r="N314" s="17"/>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:14">
       <c r="A315" s="13"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
@@ -7951,7 +8001,7 @@
       <c r="M315" s="16"/>
       <c r="N315" s="17"/>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:14">
       <c r="A316" s="13"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
@@ -7973,7 +8023,7 @@
       <c r="M316" s="16"/>
       <c r="N316" s="17"/>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:14">
       <c r="A317" s="13"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
@@ -7995,7 +8045,7 @@
       <c r="M317" s="16"/>
       <c r="N317" s="17"/>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:14">
       <c r="A318" s="13"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
@@ -8017,7 +8067,7 @@
       <c r="M318" s="16"/>
       <c r="N318" s="17"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:14">
       <c r="A319" s="13"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
@@ -8039,7 +8089,7 @@
       <c r="M319" s="16"/>
       <c r="N319" s="17"/>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:14">
       <c r="A320" s="13"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
@@ -8061,7 +8111,7 @@
       <c r="M320" s="16"/>
       <c r="N320" s="17"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:14">
       <c r="A321" s="13"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
@@ -8083,7 +8133,7 @@
       <c r="M321" s="16"/>
       <c r="N321" s="17"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:14">
       <c r="A322" s="13"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
@@ -8105,7 +8155,7 @@
       <c r="M322" s="16"/>
       <c r="N322" s="17"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:14">
       <c r="A323" s="13"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
@@ -8127,7 +8177,7 @@
       <c r="M323" s="16"/>
       <c r="N323" s="17"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:14">
       <c r="A324" s="13"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
@@ -8149,7 +8199,7 @@
       <c r="M324" s="16"/>
       <c r="N324" s="17"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:14">
       <c r="A325" s="13"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
@@ -8171,7 +8221,7 @@
       <c r="M325" s="16"/>
       <c r="N325" s="17"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:14">
       <c r="A326" s="13"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
@@ -8193,7 +8243,7 @@
       <c r="M326" s="16"/>
       <c r="N326" s="17"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:14">
       <c r="A327" s="13"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
@@ -8215,7 +8265,7 @@
       <c r="M327" s="16"/>
       <c r="N327" s="17"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:14">
       <c r="A328" s="13"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
@@ -8237,7 +8287,7 @@
       <c r="M328" s="16"/>
       <c r="N328" s="17"/>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:14">
       <c r="A329" s="13"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
@@ -8259,7 +8309,7 @@
       <c r="M329" s="16"/>
       <c r="N329" s="17"/>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:14">
       <c r="A330" s="13"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
@@ -8281,7 +8331,7 @@
       <c r="M330" s="16"/>
       <c r="N330" s="17"/>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:14">
       <c r="A331" s="13"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
@@ -8303,7 +8353,7 @@
       <c r="M331" s="16"/>
       <c r="N331" s="17"/>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:14">
       <c r="A332" s="13"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
@@ -8325,7 +8375,7 @@
       <c r="M332" s="16"/>
       <c r="N332" s="17"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:14">
       <c r="A333" s="13"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
@@ -8347,7 +8397,7 @@
       <c r="M333" s="16"/>
       <c r="N333" s="17"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:14">
       <c r="A334" s="13"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
@@ -8369,7 +8419,7 @@
       <c r="M334" s="16"/>
       <c r="N334" s="17"/>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:14">
       <c r="A335" s="13"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
@@ -8391,7 +8441,7 @@
       <c r="M335" s="16"/>
       <c r="N335" s="17"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:14">
       <c r="A336" s="13"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
@@ -8413,7 +8463,7 @@
       <c r="M336" s="16"/>
       <c r="N336" s="17"/>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:14">
       <c r="A337" s="13"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
@@ -8435,7 +8485,7 @@
       <c r="M337" s="16"/>
       <c r="N337" s="17"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:14">
       <c r="A338" s="13"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
@@ -8457,7 +8507,7 @@
       <c r="M338" s="16"/>
       <c r="N338" s="17"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:14">
       <c r="A339" s="13"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
@@ -8479,7 +8529,7 @@
       <c r="M339" s="16"/>
       <c r="N339" s="17"/>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:14">
       <c r="A340" s="13"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
@@ -8501,7 +8551,7 @@
       <c r="M340" s="16"/>
       <c r="N340" s="17"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:14">
       <c r="A341" s="13"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
@@ -8523,7 +8573,7 @@
       <c r="M341" s="16"/>
       <c r="N341" s="17"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:14">
       <c r="A342" s="13"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
@@ -8545,7 +8595,7 @@
       <c r="M342" s="16"/>
       <c r="N342" s="17"/>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:14">
       <c r="A343" s="13"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
@@ -8567,7 +8617,7 @@
       <c r="M343" s="16"/>
       <c r="N343" s="17"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:14">
       <c r="A344" s="13"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
@@ -8589,7 +8639,7 @@
       <c r="M344" s="16"/>
       <c r="N344" s="17"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:14">
       <c r="A345" s="13"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
@@ -8611,7 +8661,7 @@
       <c r="M345" s="16"/>
       <c r="N345" s="17"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:14">
       <c r="A346" s="13"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
@@ -8633,7 +8683,7 @@
       <c r="M346" s="16"/>
       <c r="N346" s="17"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:14">
       <c r="A347" s="13"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
@@ -8655,7 +8705,7 @@
       <c r="M347" s="16"/>
       <c r="N347" s="17"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:14">
       <c r="A348" s="13"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
@@ -8677,7 +8727,7 @@
       <c r="M348" s="16"/>
       <c r="N348" s="17"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:14">
       <c r="A349" s="13"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
@@ -8699,7 +8749,7 @@
       <c r="M349" s="16"/>
       <c r="N349" s="17"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:14">
       <c r="A350" s="13"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
@@ -8721,7 +8771,7 @@
       <c r="M350" s="16"/>
       <c r="N350" s="17"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:14">
       <c r="A351" s="13"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
@@ -8743,7 +8793,7 @@
       <c r="M351" s="16"/>
       <c r="N351" s="17"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:14">
       <c r="A352" s="13"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
@@ -8765,7 +8815,7 @@
       <c r="M352" s="16"/>
       <c r="N352" s="17"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:14">
       <c r="A353" s="13"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
@@ -8787,7 +8837,7 @@
       <c r="M353" s="16"/>
       <c r="N353" s="17"/>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:14">
       <c r="A354" s="13"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
@@ -8809,7 +8859,7 @@
       <c r="M354" s="16"/>
       <c r="N354" s="17"/>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:14">
       <c r="A355" s="13"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
@@ -8831,7 +8881,7 @@
       <c r="M355" s="16"/>
       <c r="N355" s="17"/>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:14">
       <c r="A356" s="13"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
@@ -8853,7 +8903,7 @@
       <c r="M356" s="16"/>
       <c r="N356" s="17"/>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:14">
       <c r="A357" s="13"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
@@ -8875,7 +8925,7 @@
       <c r="M357" s="16"/>
       <c r="N357" s="17"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:14">
       <c r="A358" s="13"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
@@ -8897,7 +8947,7 @@
       <c r="M358" s="16"/>
       <c r="N358" s="17"/>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:14">
       <c r="A359" s="13"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
@@ -8919,7 +8969,7 @@
       <c r="M359" s="16"/>
       <c r="N359" s="17"/>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:14">
       <c r="A360" s="13"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
@@ -8941,7 +8991,7 @@
       <c r="M360" s="16"/>
       <c r="N360" s="17"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:14">
       <c r="A361" s="13"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
@@ -8963,7 +9013,7 @@
       <c r="M361" s="16"/>
       <c r="N361" s="17"/>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:14">
       <c r="A362" s="13"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
@@ -8985,7 +9035,7 @@
       <c r="M362" s="16"/>
       <c r="N362" s="17"/>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:14">
       <c r="A363" s="13"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
@@ -9007,7 +9057,7 @@
       <c r="M363" s="16"/>
       <c r="N363" s="17"/>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:14">
       <c r="A364" s="13"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
@@ -9029,7 +9079,7 @@
       <c r="M364" s="16"/>
       <c r="N364" s="17"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:14">
       <c r="A365" s="13"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
@@ -9051,7 +9101,7 @@
       <c r="M365" s="16"/>
       <c r="N365" s="17"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:14">
       <c r="A366" s="13"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
@@ -9073,7 +9123,7 @@
       <c r="M366" s="16"/>
       <c r="N366" s="17"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:14">
       <c r="A367" s="13"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
@@ -9095,7 +9145,7 @@
       <c r="M367" s="16"/>
       <c r="N367" s="17"/>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:14">
       <c r="A368" s="13"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
@@ -9117,7 +9167,7 @@
       <c r="M368" s="16"/>
       <c r="N368" s="17"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:14">
       <c r="A369" s="13"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
@@ -9139,7 +9189,7 @@
       <c r="M369" s="16"/>
       <c r="N369" s="17"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:14">
       <c r="A370" s="13"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
@@ -9161,7 +9211,7 @@
       <c r="M370" s="16"/>
       <c r="N370" s="17"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:14">
       <c r="A371" s="13"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
@@ -9183,7 +9233,7 @@
       <c r="M371" s="16"/>
       <c r="N371" s="17"/>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:14">
       <c r="A372" s="13"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
@@ -9205,7 +9255,7 @@
       <c r="M372" s="16"/>
       <c r="N372" s="17"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:14">
       <c r="A373" s="13"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
@@ -9227,7 +9277,7 @@
       <c r="M373" s="16"/>
       <c r="N373" s="17"/>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:14">
       <c r="A374" s="13"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
@@ -9249,7 +9299,7 @@
       <c r="M374" s="16"/>
       <c r="N374" s="17"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:14">
       <c r="A375" s="13"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
@@ -9271,7 +9321,7 @@
       <c r="M375" s="16"/>
       <c r="N375" s="17"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:14">
       <c r="A376" s="13"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
@@ -9293,7 +9343,7 @@
       <c r="M376" s="16"/>
       <c r="N376" s="17"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:14">
       <c r="A377" s="13"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
@@ -9315,7 +9365,7 @@
       <c r="M377" s="16"/>
       <c r="N377" s="17"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:14">
       <c r="A378" s="13"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
@@ -9337,7 +9387,7 @@
       <c r="M378" s="16"/>
       <c r="N378" s="17"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:14">
       <c r="A379" s="13"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
@@ -9359,7 +9409,7 @@
       <c r="M379" s="16"/>
       <c r="N379" s="17"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:14">
       <c r="A380" s="13"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
@@ -9381,7 +9431,7 @@
       <c r="M380" s="16"/>
       <c r="N380" s="17"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:14">
       <c r="A381" s="13"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
@@ -9403,7 +9453,7 @@
       <c r="M381" s="16"/>
       <c r="N381" s="17"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:14">
       <c r="A382" s="13"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
@@ -9425,7 +9475,7 @@
       <c r="M382" s="16"/>
       <c r="N382" s="17"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:14">
       <c r="A383" s="13"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
@@ -9447,7 +9497,7 @@
       <c r="M383" s="16"/>
       <c r="N383" s="17"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:14">
       <c r="A384" s="13"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -9469,7 +9519,7 @@
       <c r="M384" s="16"/>
       <c r="N384" s="17"/>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:14">
       <c r="A385" s="13"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
@@ -9491,7 +9541,7 @@
       <c r="M385" s="16"/>
       <c r="N385" s="17"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:14">
       <c r="A386" s="13"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -9513,7 +9563,7 @@
       <c r="M386" s="16"/>
       <c r="N386" s="17"/>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:14">
       <c r="A387" s="13"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -9535,7 +9585,7 @@
       <c r="M387" s="16"/>
       <c r="N387" s="17"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:14">
       <c r="A388" s="13"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -9557,7 +9607,7 @@
       <c r="M388" s="16"/>
       <c r="N388" s="17"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:14">
       <c r="A389" s="13"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
@@ -9579,7 +9629,7 @@
       <c r="M389" s="16"/>
       <c r="N389" s="17"/>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:14">
       <c r="A390" s="13"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
@@ -9601,7 +9651,7 @@
       <c r="M390" s="16"/>
       <c r="N390" s="17"/>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:14">
       <c r="A391" s="13"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
@@ -9623,7 +9673,7 @@
       <c r="M391" s="16"/>
       <c r="N391" s="17"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:14">
       <c r="A392" s="13"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -9645,7 +9695,7 @@
       <c r="M392" s="16"/>
       <c r="N392" s="17"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:14">
       <c r="A393" s="13"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
@@ -9667,7 +9717,7 @@
       <c r="M393" s="16"/>
       <c r="N393" s="17"/>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:14">
       <c r="A394" s="13"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -9689,7 +9739,7 @@
       <c r="M394" s="16"/>
       <c r="N394" s="17"/>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:14">
       <c r="A395" s="13"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -9711,7 +9761,7 @@
       <c r="M395" s="16"/>
       <c r="N395" s="17"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:14">
       <c r="A396" s="13"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
@@ -9733,7 +9783,7 @@
       <c r="M396" s="16"/>
       <c r="N396" s="17"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:14">
       <c r="A397" s="13"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
@@ -9755,7 +9805,7 @@
       <c r="M397" s="16"/>
       <c r="N397" s="17"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:14">
       <c r="A398" s="13"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -9777,7 +9827,7 @@
       <c r="M398" s="16"/>
       <c r="N398" s="17"/>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:14">
       <c r="A399" s="13"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
@@ -9799,7 +9849,7 @@
       <c r="M399" s="16"/>
       <c r="N399" s="17"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:14">
       <c r="A400" s="13"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -9821,7 +9871,7 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:14">
       <c r="A401" s="13"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>

--- a/1234567.xlxs.xlsx
+++ b/1234567.xlxs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/BED19DC7E2258E89/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sachi\Desktop\CAP776\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE56FED6-253D-4C47-80EF-48B39A0E1958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F9E416-0873-47EB-B7A8-F07D1797E622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -244,7 +244,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,9 +414,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,186 +695,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.1">
+    <row r="1" spans="1:1" ht="23" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.5">
+    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
@@ -886,7 +886,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N401"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
@@ -899,77 +899,77 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-    </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+    </row>
+    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="20">
         <v>12623846</v>
       </c>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1">
+      <c r="G2" s="20"/>
+    </row>
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="19"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="20" t="s">
+      <c r="G3" s="20"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-    </row>
-    <row r="5" spans="1:14" ht="42">
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+    </row>
+    <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>39</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="29.1">
+    <row r="6" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>46252</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="13">
         <v>46253</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="43.5">
+    <row r="8" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="13">
         <v>46254</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13">
         <v>46255</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13">
         <v>46256</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13">
         <v>46257</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13">
         <v>46258</v>
       </c>
@@ -1335,29 +1335,35 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B13" s="14">
+        <v>400</v>
+      </c>
+      <c r="C13" s="14">
+        <v>50</v>
+      </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>450</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>990</v>
       </c>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -1379,7 +1385,7 @@
       <c r="M14" s="16"/>
       <c r="N14" s="17"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -1401,7 +1407,7 @@
       <c r="M15" s="16"/>
       <c r="N15" s="17"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -1423,7 +1429,7 @@
       <c r="M16" s="16"/>
       <c r="N16" s="17"/>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -1445,7 +1451,7 @@
       <c r="M17" s="16"/>
       <c r="N17" s="17"/>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
@@ -1467,7 +1473,7 @@
       <c r="M18" s="16"/>
       <c r="N18" s="17"/>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -1489,7 +1495,7 @@
       <c r="M19" s="16"/>
       <c r="N19" s="17"/>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -1511,7 +1517,7 @@
       <c r="M20" s="16"/>
       <c r="N20" s="17"/>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -1533,7 +1539,7 @@
       <c r="M21" s="16"/>
       <c r="N21" s="17"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -1555,7 +1561,7 @@
       <c r="M22" s="16"/>
       <c r="N22" s="17"/>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
@@ -1577,7 +1583,7 @@
       <c r="M23" s="16"/>
       <c r="N23" s="17"/>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -1599,7 +1605,7 @@
       <c r="M24" s="16"/>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -1621,7 +1627,7 @@
       <c r="M25" s="16"/>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -1643,7 +1649,7 @@
       <c r="M26" s="16"/>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -1665,7 +1671,7 @@
       <c r="M27" s="16"/>
       <c r="N27" s="17"/>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -1687,7 +1693,7 @@
       <c r="M28" s="16"/>
       <c r="N28" s="17"/>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -1709,7 +1715,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="17"/>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -1731,7 +1737,7 @@
       <c r="M30" s="16"/>
       <c r="N30" s="17"/>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -1753,7 +1759,7 @@
       <c r="M31" s="16"/>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -1775,7 +1781,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -1797,7 +1803,7 @@
       <c r="M33" s="16"/>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
@@ -1819,7 +1825,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -1841,7 +1847,7 @@
       <c r="M35" s="16"/>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -1863,7 +1869,7 @@
       <c r="M36" s="16"/>
       <c r="N36" s="17"/>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
@@ -1885,7 +1891,7 @@
       <c r="M37" s="16"/>
       <c r="N37" s="17"/>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -1907,7 +1913,7 @@
       <c r="M38" s="16"/>
       <c r="N38" s="17"/>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -1929,7 +1935,7 @@
       <c r="M39" s="16"/>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -1951,7 +1957,7 @@
       <c r="M40" s="16"/>
       <c r="N40" s="17"/>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="13"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
@@ -1973,7 +1979,7 @@
       <c r="M41" s="16"/>
       <c r="N41" s="17"/>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="13"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
@@ -1995,7 +2001,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="13"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -2017,7 +2023,7 @@
       <c r="M43" s="16"/>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -2039,7 +2045,7 @@
       <c r="M44" s="16"/>
       <c r="N44" s="17"/>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="13"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -2061,7 +2067,7 @@
       <c r="M45" s="16"/>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -2083,7 +2089,7 @@
       <c r="M46" s="16"/>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -2105,7 +2111,7 @@
       <c r="M47" s="16"/>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -2127,7 +2133,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -2149,7 +2155,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -2171,7 +2177,7 @@
       <c r="M50" s="16"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -2193,7 +2199,7 @@
       <c r="M51" s="16"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -2215,7 +2221,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -2237,7 +2243,7 @@
       <c r="M53" s="16"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -2259,7 +2265,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -2281,7 +2287,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -2303,7 +2309,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -2325,7 +2331,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -2347,7 +2353,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -2369,7 +2375,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="17"/>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -2391,7 +2397,7 @@
       <c r="M60" s="16"/>
       <c r="N60" s="17"/>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -2413,7 +2419,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="17"/>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -2435,7 +2441,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="17"/>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -2457,7 +2463,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="17"/>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -2479,7 +2485,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -2501,7 +2507,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="17"/>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -2523,7 +2529,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -2545,7 +2551,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="17"/>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -2567,7 +2573,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="17"/>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -2589,7 +2595,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -2611,7 +2617,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -2633,7 +2639,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="17"/>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -2655,7 +2661,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -2677,7 +2683,7 @@
       <c r="M73" s="16"/>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -2699,7 +2705,7 @@
       <c r="M74" s="16"/>
       <c r="N74" s="17"/>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -2721,7 +2727,7 @@
       <c r="M75" s="16"/>
       <c r="N75" s="17"/>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -2743,7 +2749,7 @@
       <c r="M76" s="16"/>
       <c r="N76" s="17"/>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -2765,7 +2771,7 @@
       <c r="M77" s="16"/>
       <c r="N77" s="17"/>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -2787,7 +2793,7 @@
       <c r="M78" s="16"/>
       <c r="N78" s="17"/>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -2809,7 +2815,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="17"/>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -2831,7 +2837,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="17"/>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="13"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
@@ -2853,7 +2859,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="17"/>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="13"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
@@ -2875,7 +2881,7 @@
       <c r="M82" s="16"/>
       <c r="N82" s="17"/>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
@@ -2897,7 +2903,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="17"/>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -2919,7 +2925,7 @@
       <c r="M84" s="16"/>
       <c r="N84" s="17"/>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
@@ -2941,7 +2947,7 @@
       <c r="M85" s="16"/>
       <c r="N85" s="17"/>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -2963,7 +2969,7 @@
       <c r="M86" s="16"/>
       <c r="N86" s="17"/>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -2985,7 +2991,7 @@
       <c r="M87" s="16"/>
       <c r="N87" s="17"/>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -3007,7 +3013,7 @@
       <c r="M88" s="16"/>
       <c r="N88" s="17"/>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="13"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
@@ -3029,7 +3035,7 @@
       <c r="M89" s="16"/>
       <c r="N89" s="17"/>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -3051,7 +3057,7 @@
       <c r="M90" s="16"/>
       <c r="N90" s="17"/>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
@@ -3073,7 +3079,7 @@
       <c r="M91" s="16"/>
       <c r="N91" s="17"/>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -3095,7 +3101,7 @@
       <c r="M92" s="16"/>
       <c r="N92" s="17"/>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="13"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -3117,7 +3123,7 @@
       <c r="M93" s="16"/>
       <c r="N93" s="17"/>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -3139,7 +3145,7 @@
       <c r="M94" s="16"/>
       <c r="N94" s="17"/>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -3161,7 +3167,7 @@
       <c r="M95" s="16"/>
       <c r="N95" s="17"/>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
@@ -3183,7 +3189,7 @@
       <c r="M96" s="16"/>
       <c r="N96" s="17"/>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
@@ -3205,7 +3211,7 @@
       <c r="M97" s="16"/>
       <c r="N97" s="17"/>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -3227,7 +3233,7 @@
       <c r="M98" s="16"/>
       <c r="N98" s="17"/>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
@@ -3249,7 +3255,7 @@
       <c r="M99" s="16"/>
       <c r="N99" s="17"/>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
@@ -3271,7 +3277,7 @@
       <c r="M100" s="16"/>
       <c r="N100" s="17"/>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
@@ -3293,7 +3299,7 @@
       <c r="M101" s="16"/>
       <c r="N101" s="17"/>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
@@ -3315,7 +3321,7 @@
       <c r="M102" s="16"/>
       <c r="N102" s="17"/>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
@@ -3337,7 +3343,7 @@
       <c r="M103" s="16"/>
       <c r="N103" s="17"/>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -3359,7 +3365,7 @@
       <c r="M104" s="16"/>
       <c r="N104" s="17"/>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="13"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
@@ -3381,7 +3387,7 @@
       <c r="M105" s="16"/>
       <c r="N105" s="17"/>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
@@ -3403,7 +3409,7 @@
       <c r="M106" s="16"/>
       <c r="N106" s="17"/>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" s="13"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
@@ -3425,7 +3431,7 @@
       <c r="M107" s="16"/>
       <c r="N107" s="17"/>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="13"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
@@ -3447,7 +3453,7 @@
       <c r="M108" s="16"/>
       <c r="N108" s="17"/>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
@@ -3469,7 +3475,7 @@
       <c r="M109" s="16"/>
       <c r="N109" s="17"/>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" s="13"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
@@ -3491,7 +3497,7 @@
       <c r="M110" s="16"/>
       <c r="N110" s="17"/>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
@@ -3513,7 +3519,7 @@
       <c r="M111" s="16"/>
       <c r="N111" s="17"/>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="13"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
@@ -3535,7 +3541,7 @@
       <c r="M112" s="16"/>
       <c r="N112" s="17"/>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="13"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
@@ -3557,7 +3563,7 @@
       <c r="M113" s="16"/>
       <c r="N113" s="17"/>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
@@ -3579,7 +3585,7 @@
       <c r="M114" s="16"/>
       <c r="N114" s="17"/>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="13"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
@@ -3601,7 +3607,7 @@
       <c r="M115" s="16"/>
       <c r="N115" s="17"/>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="13"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -3623,7 +3629,7 @@
       <c r="M116" s="16"/>
       <c r="N116" s="17"/>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="13"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
@@ -3645,7 +3651,7 @@
       <c r="M117" s="16"/>
       <c r="N117" s="17"/>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="13"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
@@ -3667,7 +3673,7 @@
       <c r="M118" s="16"/>
       <c r="N118" s="17"/>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="13"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
@@ -3689,7 +3695,7 @@
       <c r="M119" s="16"/>
       <c r="N119" s="17"/>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="13"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
@@ -3711,7 +3717,7 @@
       <c r="M120" s="16"/>
       <c r="N120" s="17"/>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
@@ -3733,7 +3739,7 @@
       <c r="M121" s="16"/>
       <c r="N121" s="17"/>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="13"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -3755,7 +3761,7 @@
       <c r="M122" s="16"/>
       <c r="N122" s="17"/>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="13"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -3777,7 +3783,7 @@
       <c r="M123" s="16"/>
       <c r="N123" s="17"/>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="13"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
@@ -3799,7 +3805,7 @@
       <c r="M124" s="16"/>
       <c r="N124" s="17"/>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="13"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
@@ -3821,7 +3827,7 @@
       <c r="M125" s="16"/>
       <c r="N125" s="17"/>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="13"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
@@ -3843,7 +3849,7 @@
       <c r="M126" s="16"/>
       <c r="N126" s="17"/>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="13"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -3865,7 +3871,7 @@
       <c r="M127" s="16"/>
       <c r="N127" s="17"/>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="13"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -3887,7 +3893,7 @@
       <c r="M128" s="16"/>
       <c r="N128" s="17"/>
     </row>
-    <row r="129" spans="1:14">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="13"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
@@ -3909,7 +3915,7 @@
       <c r="M129" s="16"/>
       <c r="N129" s="17"/>
     </row>
-    <row r="130" spans="1:14">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="13"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
@@ -3931,7 +3937,7 @@
       <c r="M130" s="16"/>
       <c r="N130" s="17"/>
     </row>
-    <row r="131" spans="1:14">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="13"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
@@ -3953,7 +3959,7 @@
       <c r="M131" s="16"/>
       <c r="N131" s="17"/>
     </row>
-    <row r="132" spans="1:14">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="13"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
@@ -3975,7 +3981,7 @@
       <c r="M132" s="16"/>
       <c r="N132" s="17"/>
     </row>
-    <row r="133" spans="1:14">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="13"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
@@ -3997,7 +4003,7 @@
       <c r="M133" s="16"/>
       <c r="N133" s="17"/>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -4019,7 +4025,7 @@
       <c r="M134" s="16"/>
       <c r="N134" s="17"/>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
@@ -4041,7 +4047,7 @@
       <c r="M135" s="16"/>
       <c r="N135" s="17"/>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="13"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
@@ -4063,7 +4069,7 @@
       <c r="M136" s="16"/>
       <c r="N136" s="17"/>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
@@ -4085,7 +4091,7 @@
       <c r="M137" s="16"/>
       <c r="N137" s="17"/>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="13"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
@@ -4107,7 +4113,7 @@
       <c r="M138" s="16"/>
       <c r="N138" s="17"/>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="13"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
@@ -4129,7 +4135,7 @@
       <c r="M139" s="16"/>
       <c r="N139" s="17"/>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" s="13"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
@@ -4151,7 +4157,7 @@
       <c r="M140" s="16"/>
       <c r="N140" s="17"/>
     </row>
-    <row r="141" spans="1:14">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" s="13"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
@@ -4173,7 +4179,7 @@
       <c r="M141" s="16"/>
       <c r="N141" s="17"/>
     </row>
-    <row r="142" spans="1:14">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" s="13"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
@@ -4195,7 +4201,7 @@
       <c r="M142" s="16"/>
       <c r="N142" s="17"/>
     </row>
-    <row r="143" spans="1:14">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
@@ -4217,7 +4223,7 @@
       <c r="M143" s="16"/>
       <c r="N143" s="17"/>
     </row>
-    <row r="144" spans="1:14">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" s="13"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
@@ -4239,7 +4245,7 @@
       <c r="M144" s="16"/>
       <c r="N144" s="17"/>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" s="13"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
@@ -4261,7 +4267,7 @@
       <c r="M145" s="16"/>
       <c r="N145" s="17"/>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A146" s="13"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
@@ -4283,7 +4289,7 @@
       <c r="M146" s="16"/>
       <c r="N146" s="17"/>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
@@ -4305,7 +4311,7 @@
       <c r="M147" s="16"/>
       <c r="N147" s="17"/>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" s="13"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
@@ -4327,7 +4333,7 @@
       <c r="M148" s="16"/>
       <c r="N148" s="17"/>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" s="13"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
@@ -4349,7 +4355,7 @@
       <c r="M149" s="16"/>
       <c r="N149" s="17"/>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
@@ -4371,7 +4377,7 @@
       <c r="M150" s="16"/>
       <c r="N150" s="17"/>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A151" s="13"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
@@ -4393,7 +4399,7 @@
       <c r="M151" s="16"/>
       <c r="N151" s="17"/>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" s="13"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
@@ -4415,7 +4421,7 @@
       <c r="M152" s="16"/>
       <c r="N152" s="17"/>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A153" s="13"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
@@ -4437,7 +4443,7 @@
       <c r="M153" s="16"/>
       <c r="N153" s="17"/>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A154" s="13"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
@@ -4459,7 +4465,7 @@
       <c r="M154" s="16"/>
       <c r="N154" s="17"/>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A155" s="13"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
@@ -4481,7 +4487,7 @@
       <c r="M155" s="16"/>
       <c r="N155" s="17"/>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A156" s="13"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
@@ -4503,7 +4509,7 @@
       <c r="M156" s="16"/>
       <c r="N156" s="17"/>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A157" s="13"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
@@ -4525,7 +4531,7 @@
       <c r="M157" s="16"/>
       <c r="N157" s="17"/>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A158" s="13"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
@@ -4547,7 +4553,7 @@
       <c r="M158" s="16"/>
       <c r="N158" s="17"/>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A159" s="13"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
@@ -4569,7 +4575,7 @@
       <c r="M159" s="16"/>
       <c r="N159" s="17"/>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A160" s="13"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
@@ -4591,7 +4597,7 @@
       <c r="M160" s="16"/>
       <c r="N160" s="17"/>
     </row>
-    <row r="161" spans="1:14">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A161" s="13"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
@@ -4613,7 +4619,7 @@
       <c r="M161" s="16"/>
       <c r="N161" s="17"/>
     </row>
-    <row r="162" spans="1:14">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A162" s="13"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
@@ -4635,7 +4641,7 @@
       <c r="M162" s="16"/>
       <c r="N162" s="17"/>
     </row>
-    <row r="163" spans="1:14">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A163" s="13"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
@@ -4657,7 +4663,7 @@
       <c r="M163" s="16"/>
       <c r="N163" s="17"/>
     </row>
-    <row r="164" spans="1:14">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A164" s="13"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
@@ -4679,7 +4685,7 @@
       <c r="M164" s="16"/>
       <c r="N164" s="17"/>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A165" s="13"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
@@ -4701,7 +4707,7 @@
       <c r="M165" s="16"/>
       <c r="N165" s="17"/>
     </row>
-    <row r="166" spans="1:14">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A166" s="13"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
@@ -4723,7 +4729,7 @@
       <c r="M166" s="16"/>
       <c r="N166" s="17"/>
     </row>
-    <row r="167" spans="1:14">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A167" s="13"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
@@ -4745,7 +4751,7 @@
       <c r="M167" s="16"/>
       <c r="N167" s="17"/>
     </row>
-    <row r="168" spans="1:14">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A168" s="13"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
@@ -4767,7 +4773,7 @@
       <c r="M168" s="16"/>
       <c r="N168" s="17"/>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A169" s="13"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
@@ -4789,7 +4795,7 @@
       <c r="M169" s="16"/>
       <c r="N169" s="17"/>
     </row>
-    <row r="170" spans="1:14">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A170" s="13"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
@@ -4811,7 +4817,7 @@
       <c r="M170" s="16"/>
       <c r="N170" s="17"/>
     </row>
-    <row r="171" spans="1:14">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A171" s="13"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
@@ -4833,7 +4839,7 @@
       <c r="M171" s="16"/>
       <c r="N171" s="17"/>
     </row>
-    <row r="172" spans="1:14">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A172" s="13"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
@@ -4855,7 +4861,7 @@
       <c r="M172" s="16"/>
       <c r="N172" s="17"/>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A173" s="13"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
@@ -4877,7 +4883,7 @@
       <c r="M173" s="16"/>
       <c r="N173" s="17"/>
     </row>
-    <row r="174" spans="1:14">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
@@ -4899,7 +4905,7 @@
       <c r="M174" s="16"/>
       <c r="N174" s="17"/>
     </row>
-    <row r="175" spans="1:14">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A175" s="13"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
@@ -4921,7 +4927,7 @@
       <c r="M175" s="16"/>
       <c r="N175" s="17"/>
     </row>
-    <row r="176" spans="1:14">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A176" s="13"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
@@ -4943,7 +4949,7 @@
       <c r="M176" s="16"/>
       <c r="N176" s="17"/>
     </row>
-    <row r="177" spans="1:14">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A177" s="13"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
@@ -4965,7 +4971,7 @@
       <c r="M177" s="16"/>
       <c r="N177" s="17"/>
     </row>
-    <row r="178" spans="1:14">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A178" s="13"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
@@ -4987,7 +4993,7 @@
       <c r="M178" s="16"/>
       <c r="N178" s="17"/>
     </row>
-    <row r="179" spans="1:14">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A179" s="13"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
@@ -5009,7 +5015,7 @@
       <c r="M179" s="16"/>
       <c r="N179" s="17"/>
     </row>
-    <row r="180" spans="1:14">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A180" s="13"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
@@ -5031,7 +5037,7 @@
       <c r="M180" s="16"/>
       <c r="N180" s="17"/>
     </row>
-    <row r="181" spans="1:14">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A181" s="13"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
@@ -5053,7 +5059,7 @@
       <c r="M181" s="16"/>
       <c r="N181" s="17"/>
     </row>
-    <row r="182" spans="1:14">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A182" s="13"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -5075,7 +5081,7 @@
       <c r="M182" s="16"/>
       <c r="N182" s="17"/>
     </row>
-    <row r="183" spans="1:14">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A183" s="13"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
@@ -5097,7 +5103,7 @@
       <c r="M183" s="16"/>
       <c r="N183" s="17"/>
     </row>
-    <row r="184" spans="1:14">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A184" s="13"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
@@ -5119,7 +5125,7 @@
       <c r="M184" s="16"/>
       <c r="N184" s="17"/>
     </row>
-    <row r="185" spans="1:14">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A185" s="13"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
@@ -5141,7 +5147,7 @@
       <c r="M185" s="16"/>
       <c r="N185" s="17"/>
     </row>
-    <row r="186" spans="1:14">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A186" s="13"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -5163,7 +5169,7 @@
       <c r="M186" s="16"/>
       <c r="N186" s="17"/>
     </row>
-    <row r="187" spans="1:14">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A187" s="13"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
@@ -5185,7 +5191,7 @@
       <c r="M187" s="16"/>
       <c r="N187" s="17"/>
     </row>
-    <row r="188" spans="1:14">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A188" s="13"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
@@ -5207,7 +5213,7 @@
       <c r="M188" s="16"/>
       <c r="N188" s="17"/>
     </row>
-    <row r="189" spans="1:14">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A189" s="13"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
@@ -5229,7 +5235,7 @@
       <c r="M189" s="16"/>
       <c r="N189" s="17"/>
     </row>
-    <row r="190" spans="1:14">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A190" s="13"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
@@ -5251,7 +5257,7 @@
       <c r="M190" s="16"/>
       <c r="N190" s="17"/>
     </row>
-    <row r="191" spans="1:14">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A191" s="13"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
@@ -5273,7 +5279,7 @@
       <c r="M191" s="16"/>
       <c r="N191" s="17"/>
     </row>
-    <row r="192" spans="1:14">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A192" s="13"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -5295,7 +5301,7 @@
       <c r="M192" s="16"/>
       <c r="N192" s="17"/>
     </row>
-    <row r="193" spans="1:14">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -5317,7 +5323,7 @@
       <c r="M193" s="16"/>
       <c r="N193" s="17"/>
     </row>
-    <row r="194" spans="1:14">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A194" s="13"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -5339,7 +5345,7 @@
       <c r="M194" s="16"/>
       <c r="N194" s="17"/>
     </row>
-    <row r="195" spans="1:14">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A195" s="13"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
@@ -5361,7 +5367,7 @@
       <c r="M195" s="16"/>
       <c r="N195" s="17"/>
     </row>
-    <row r="196" spans="1:14">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A196" s="13"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
@@ -5383,7 +5389,7 @@
       <c r="M196" s="16"/>
       <c r="N196" s="17"/>
     </row>
-    <row r="197" spans="1:14">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A197" s="13"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
@@ -5405,7 +5411,7 @@
       <c r="M197" s="16"/>
       <c r="N197" s="17"/>
     </row>
-    <row r="198" spans="1:14">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A198" s="13"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
@@ -5427,7 +5433,7 @@
       <c r="M198" s="16"/>
       <c r="N198" s="17"/>
     </row>
-    <row r="199" spans="1:14">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A199" s="13"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
@@ -5449,7 +5455,7 @@
       <c r="M199" s="16"/>
       <c r="N199" s="17"/>
     </row>
-    <row r="200" spans="1:14">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A200" s="13"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
@@ -5471,7 +5477,7 @@
       <c r="M200" s="16"/>
       <c r="N200" s="17"/>
     </row>
-    <row r="201" spans="1:14">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A201" s="13"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
@@ -5493,7 +5499,7 @@
       <c r="M201" s="16"/>
       <c r="N201" s="17"/>
     </row>
-    <row r="202" spans="1:14">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A202" s="13"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -5515,7 +5521,7 @@
       <c r="M202" s="16"/>
       <c r="N202" s="17"/>
     </row>
-    <row r="203" spans="1:14">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A203" s="13"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
@@ -5537,7 +5543,7 @@
       <c r="M203" s="16"/>
       <c r="N203" s="17"/>
     </row>
-    <row r="204" spans="1:14">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A204" s="13"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
@@ -5559,7 +5565,7 @@
       <c r="M204" s="16"/>
       <c r="N204" s="17"/>
     </row>
-    <row r="205" spans="1:14">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A205" s="13"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
@@ -5581,7 +5587,7 @@
       <c r="M205" s="16"/>
       <c r="N205" s="17"/>
     </row>
-    <row r="206" spans="1:14">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A206" s="13"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
@@ -5603,7 +5609,7 @@
       <c r="M206" s="16"/>
       <c r="N206" s="17"/>
     </row>
-    <row r="207" spans="1:14">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A207" s="13"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
@@ -5625,7 +5631,7 @@
       <c r="M207" s="16"/>
       <c r="N207" s="17"/>
     </row>
-    <row r="208" spans="1:14">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A208" s="13"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
@@ -5647,7 +5653,7 @@
       <c r="M208" s="16"/>
       <c r="N208" s="17"/>
     </row>
-    <row r="209" spans="1:14">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A209" s="13"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
@@ -5669,7 +5675,7 @@
       <c r="M209" s="16"/>
       <c r="N209" s="17"/>
     </row>
-    <row r="210" spans="1:14">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A210" s="13"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
@@ -5691,7 +5697,7 @@
       <c r="M210" s="16"/>
       <c r="N210" s="17"/>
     </row>
-    <row r="211" spans="1:14">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A211" s="13"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
@@ -5713,7 +5719,7 @@
       <c r="M211" s="16"/>
       <c r="N211" s="17"/>
     </row>
-    <row r="212" spans="1:14">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A212" s="13"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
@@ -5735,7 +5741,7 @@
       <c r="M212" s="16"/>
       <c r="N212" s="17"/>
     </row>
-    <row r="213" spans="1:14">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
@@ -5757,7 +5763,7 @@
       <c r="M213" s="16"/>
       <c r="N213" s="17"/>
     </row>
-    <row r="214" spans="1:14">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A214" s="13"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
@@ -5779,7 +5785,7 @@
       <c r="M214" s="16"/>
       <c r="N214" s="17"/>
     </row>
-    <row r="215" spans="1:14">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A215" s="13"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
@@ -5801,7 +5807,7 @@
       <c r="M215" s="16"/>
       <c r="N215" s="17"/>
     </row>
-    <row r="216" spans="1:14">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A216" s="13"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
@@ -5823,7 +5829,7 @@
       <c r="M216" s="16"/>
       <c r="N216" s="17"/>
     </row>
-    <row r="217" spans="1:14">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A217" s="13"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
@@ -5845,7 +5851,7 @@
       <c r="M217" s="16"/>
       <c r="N217" s="17"/>
     </row>
-    <row r="218" spans="1:14">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A218" s="13"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
@@ -5867,7 +5873,7 @@
       <c r="M218" s="16"/>
       <c r="N218" s="17"/>
     </row>
-    <row r="219" spans="1:14">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A219" s="13"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
@@ -5889,7 +5895,7 @@
       <c r="M219" s="16"/>
       <c r="N219" s="17"/>
     </row>
-    <row r="220" spans="1:14">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A220" s="13"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
@@ -5911,7 +5917,7 @@
       <c r="M220" s="16"/>
       <c r="N220" s="17"/>
     </row>
-    <row r="221" spans="1:14">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A221" s="13"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
@@ -5933,7 +5939,7 @@
       <c r="M221" s="16"/>
       <c r="N221" s="17"/>
     </row>
-    <row r="222" spans="1:14">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A222" s="13"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
@@ -5955,7 +5961,7 @@
       <c r="M222" s="16"/>
       <c r="N222" s="17"/>
     </row>
-    <row r="223" spans="1:14">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A223" s="13"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
@@ -5977,7 +5983,7 @@
       <c r="M223" s="16"/>
       <c r="N223" s="17"/>
     </row>
-    <row r="224" spans="1:14">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A224" s="13"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
@@ -5999,7 +6005,7 @@
       <c r="M224" s="16"/>
       <c r="N224" s="17"/>
     </row>
-    <row r="225" spans="1:14">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A225" s="13"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
@@ -6021,7 +6027,7 @@
       <c r="M225" s="16"/>
       <c r="N225" s="17"/>
     </row>
-    <row r="226" spans="1:14">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A226" s="13"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
@@ -6043,7 +6049,7 @@
       <c r="M226" s="16"/>
       <c r="N226" s="17"/>
     </row>
-    <row r="227" spans="1:14">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A227" s="13"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
@@ -6065,7 +6071,7 @@
       <c r="M227" s="16"/>
       <c r="N227" s="17"/>
     </row>
-    <row r="228" spans="1:14">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A228" s="13"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
@@ -6087,7 +6093,7 @@
       <c r="M228" s="16"/>
       <c r="N228" s="17"/>
     </row>
-    <row r="229" spans="1:14">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A229" s="13"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
@@ -6109,7 +6115,7 @@
       <c r="M229" s="16"/>
       <c r="N229" s="17"/>
     </row>
-    <row r="230" spans="1:14">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A230" s="13"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
@@ -6131,7 +6137,7 @@
       <c r="M230" s="16"/>
       <c r="N230" s="17"/>
     </row>
-    <row r="231" spans="1:14">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A231" s="13"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
@@ -6153,7 +6159,7 @@
       <c r="M231" s="16"/>
       <c r="N231" s="17"/>
     </row>
-    <row r="232" spans="1:14">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A232" s="13"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
@@ -6175,7 +6181,7 @@
       <c r="M232" s="16"/>
       <c r="N232" s="17"/>
     </row>
-    <row r="233" spans="1:14">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A233" s="13"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
@@ -6197,7 +6203,7 @@
       <c r="M233" s="16"/>
       <c r="N233" s="17"/>
     </row>
-    <row r="234" spans="1:14">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A234" s="13"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
@@ -6219,7 +6225,7 @@
       <c r="M234" s="16"/>
       <c r="N234" s="17"/>
     </row>
-    <row r="235" spans="1:14">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A235" s="13"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
@@ -6241,7 +6247,7 @@
       <c r="M235" s="16"/>
       <c r="N235" s="17"/>
     </row>
-    <row r="236" spans="1:14">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A236" s="13"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
@@ -6263,7 +6269,7 @@
       <c r="M236" s="16"/>
       <c r="N236" s="17"/>
     </row>
-    <row r="237" spans="1:14">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A237" s="13"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
@@ -6285,7 +6291,7 @@
       <c r="M237" s="16"/>
       <c r="N237" s="17"/>
     </row>
-    <row r="238" spans="1:14">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A238" s="13"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
@@ -6307,7 +6313,7 @@
       <c r="M238" s="16"/>
       <c r="N238" s="17"/>
     </row>
-    <row r="239" spans="1:14">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A239" s="13"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
@@ -6329,7 +6335,7 @@
       <c r="M239" s="16"/>
       <c r="N239" s="17"/>
     </row>
-    <row r="240" spans="1:14">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A240" s="13"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
@@ -6351,7 +6357,7 @@
       <c r="M240" s="16"/>
       <c r="N240" s="17"/>
     </row>
-    <row r="241" spans="1:14">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A241" s="13"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
@@ -6373,7 +6379,7 @@
       <c r="M241" s="16"/>
       <c r="N241" s="17"/>
     </row>
-    <row r="242" spans="1:14">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A242" s="13"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
@@ -6395,7 +6401,7 @@
       <c r="M242" s="16"/>
       <c r="N242" s="17"/>
     </row>
-    <row r="243" spans="1:14">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A243" s="13"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
@@ -6417,7 +6423,7 @@
       <c r="M243" s="16"/>
       <c r="N243" s="17"/>
     </row>
-    <row r="244" spans="1:14">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A244" s="13"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
@@ -6439,7 +6445,7 @@
       <c r="M244" s="16"/>
       <c r="N244" s="17"/>
     </row>
-    <row r="245" spans="1:14">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A245" s="13"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
@@ -6461,7 +6467,7 @@
       <c r="M245" s="16"/>
       <c r="N245" s="17"/>
     </row>
-    <row r="246" spans="1:14">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A246" s="13"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
@@ -6483,7 +6489,7 @@
       <c r="M246" s="16"/>
       <c r="N246" s="17"/>
     </row>
-    <row r="247" spans="1:14">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A247" s="13"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
@@ -6505,7 +6511,7 @@
       <c r="M247" s="16"/>
       <c r="N247" s="17"/>
     </row>
-    <row r="248" spans="1:14">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A248" s="13"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
@@ -6527,7 +6533,7 @@
       <c r="M248" s="16"/>
       <c r="N248" s="17"/>
     </row>
-    <row r="249" spans="1:14">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A249" s="13"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
@@ -6549,7 +6555,7 @@
       <c r="M249" s="16"/>
       <c r="N249" s="17"/>
     </row>
-    <row r="250" spans="1:14">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A250" s="13"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
@@ -6571,7 +6577,7 @@
       <c r="M250" s="16"/>
       <c r="N250" s="17"/>
     </row>
-    <row r="251" spans="1:14">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A251" s="13"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
@@ -6593,7 +6599,7 @@
       <c r="M251" s="16"/>
       <c r="N251" s="17"/>
     </row>
-    <row r="252" spans="1:14">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A252" s="13"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
@@ -6615,7 +6621,7 @@
       <c r="M252" s="16"/>
       <c r="N252" s="17"/>
     </row>
-    <row r="253" spans="1:14">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A253" s="13"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
@@ -6637,7 +6643,7 @@
       <c r="M253" s="16"/>
       <c r="N253" s="17"/>
     </row>
-    <row r="254" spans="1:14">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A254" s="13"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
@@ -6659,7 +6665,7 @@
       <c r="M254" s="16"/>
       <c r="N254" s="17"/>
     </row>
-    <row r="255" spans="1:14">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A255" s="13"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
@@ -6681,7 +6687,7 @@
       <c r="M255" s="16"/>
       <c r="N255" s="17"/>
     </row>
-    <row r="256" spans="1:14">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A256" s="13"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
@@ -6703,7 +6709,7 @@
       <c r="M256" s="16"/>
       <c r="N256" s="17"/>
     </row>
-    <row r="257" spans="1:14">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A257" s="13"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
@@ -6725,7 +6731,7 @@
       <c r="M257" s="16"/>
       <c r="N257" s="17"/>
     </row>
-    <row r="258" spans="1:14">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A258" s="13"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
@@ -6747,7 +6753,7 @@
       <c r="M258" s="16"/>
       <c r="N258" s="17"/>
     </row>
-    <row r="259" spans="1:14">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A259" s="13"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
@@ -6769,7 +6775,7 @@
       <c r="M259" s="16"/>
       <c r="N259" s="17"/>
     </row>
-    <row r="260" spans="1:14">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A260" s="13"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
@@ -6791,7 +6797,7 @@
       <c r="M260" s="16"/>
       <c r="N260" s="17"/>
     </row>
-    <row r="261" spans="1:14">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A261" s="13"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
@@ -6813,7 +6819,7 @@
       <c r="M261" s="16"/>
       <c r="N261" s="17"/>
     </row>
-    <row r="262" spans="1:14">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A262" s="13"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
@@ -6835,7 +6841,7 @@
       <c r="M262" s="16"/>
       <c r="N262" s="17"/>
     </row>
-    <row r="263" spans="1:14">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A263" s="13"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
@@ -6857,7 +6863,7 @@
       <c r="M263" s="16"/>
       <c r="N263" s="17"/>
     </row>
-    <row r="264" spans="1:14">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A264" s="13"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
@@ -6879,7 +6885,7 @@
       <c r="M264" s="16"/>
       <c r="N264" s="17"/>
     </row>
-    <row r="265" spans="1:14">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A265" s="13"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
@@ -6901,7 +6907,7 @@
       <c r="M265" s="16"/>
       <c r="N265" s="17"/>
     </row>
-    <row r="266" spans="1:14">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A266" s="13"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
@@ -6923,7 +6929,7 @@
       <c r="M266" s="16"/>
       <c r="N266" s="17"/>
     </row>
-    <row r="267" spans="1:14">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A267" s="13"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
@@ -6945,7 +6951,7 @@
       <c r="M267" s="16"/>
       <c r="N267" s="17"/>
     </row>
-    <row r="268" spans="1:14">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A268" s="13"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
@@ -6967,7 +6973,7 @@
       <c r="M268" s="16"/>
       <c r="N268" s="17"/>
     </row>
-    <row r="269" spans="1:14">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A269" s="13"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
@@ -6989,7 +6995,7 @@
       <c r="M269" s="16"/>
       <c r="N269" s="17"/>
     </row>
-    <row r="270" spans="1:14">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A270" s="13"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
@@ -7011,7 +7017,7 @@
       <c r="M270" s="16"/>
       <c r="N270" s="17"/>
     </row>
-    <row r="271" spans="1:14">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A271" s="13"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
@@ -7033,7 +7039,7 @@
       <c r="M271" s="16"/>
       <c r="N271" s="17"/>
     </row>
-    <row r="272" spans="1:14">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A272" s="13"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
@@ -7055,7 +7061,7 @@
       <c r="M272" s="16"/>
       <c r="N272" s="17"/>
     </row>
-    <row r="273" spans="1:14">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A273" s="13"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
@@ -7077,7 +7083,7 @@
       <c r="M273" s="16"/>
       <c r="N273" s="17"/>
     </row>
-    <row r="274" spans="1:14">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A274" s="13"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
@@ -7099,7 +7105,7 @@
       <c r="M274" s="16"/>
       <c r="N274" s="17"/>
     </row>
-    <row r="275" spans="1:14">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A275" s="13"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
@@ -7121,7 +7127,7 @@
       <c r="M275" s="16"/>
       <c r="N275" s="17"/>
     </row>
-    <row r="276" spans="1:14">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A276" s="13"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
@@ -7143,7 +7149,7 @@
       <c r="M276" s="16"/>
       <c r="N276" s="17"/>
     </row>
-    <row r="277" spans="1:14">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A277" s="13"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
@@ -7165,7 +7171,7 @@
       <c r="M277" s="16"/>
       <c r="N277" s="17"/>
     </row>
-    <row r="278" spans="1:14">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A278" s="13"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
@@ -7187,7 +7193,7 @@
       <c r="M278" s="16"/>
       <c r="N278" s="17"/>
     </row>
-    <row r="279" spans="1:14">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A279" s="13"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
@@ -7209,7 +7215,7 @@
       <c r="M279" s="16"/>
       <c r="N279" s="17"/>
     </row>
-    <row r="280" spans="1:14">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A280" s="13"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
@@ -7231,7 +7237,7 @@
       <c r="M280" s="16"/>
       <c r="N280" s="17"/>
     </row>
-    <row r="281" spans="1:14">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A281" s="13"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
@@ -7253,7 +7259,7 @@
       <c r="M281" s="16"/>
       <c r="N281" s="17"/>
     </row>
-    <row r="282" spans="1:14">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A282" s="13"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
@@ -7275,7 +7281,7 @@
       <c r="M282" s="16"/>
       <c r="N282" s="17"/>
     </row>
-    <row r="283" spans="1:14">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A283" s="13"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
@@ -7297,7 +7303,7 @@
       <c r="M283" s="16"/>
       <c r="N283" s="17"/>
     </row>
-    <row r="284" spans="1:14">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A284" s="13"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
@@ -7319,7 +7325,7 @@
       <c r="M284" s="16"/>
       <c r="N284" s="17"/>
     </row>
-    <row r="285" spans="1:14">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A285" s="13"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
@@ -7341,7 +7347,7 @@
       <c r="M285" s="16"/>
       <c r="N285" s="17"/>
     </row>
-    <row r="286" spans="1:14">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A286" s="13"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
@@ -7363,7 +7369,7 @@
       <c r="M286" s="16"/>
       <c r="N286" s="17"/>
     </row>
-    <row r="287" spans="1:14">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A287" s="13"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
@@ -7385,7 +7391,7 @@
       <c r="M287" s="16"/>
       <c r="N287" s="17"/>
     </row>
-    <row r="288" spans="1:14">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A288" s="13"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
@@ -7407,7 +7413,7 @@
       <c r="M288" s="16"/>
       <c r="N288" s="17"/>
     </row>
-    <row r="289" spans="1:14">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A289" s="13"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
@@ -7429,7 +7435,7 @@
       <c r="M289" s="16"/>
       <c r="N289" s="17"/>
     </row>
-    <row r="290" spans="1:14">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A290" s="13"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
@@ -7451,7 +7457,7 @@
       <c r="M290" s="16"/>
       <c r="N290" s="17"/>
     </row>
-    <row r="291" spans="1:14">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A291" s="13"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
@@ -7473,7 +7479,7 @@
       <c r="M291" s="16"/>
       <c r="N291" s="17"/>
     </row>
-    <row r="292" spans="1:14">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A292" s="13"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
@@ -7495,7 +7501,7 @@
       <c r="M292" s="16"/>
       <c r="N292" s="17"/>
     </row>
-    <row r="293" spans="1:14">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A293" s="13"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
@@ -7517,7 +7523,7 @@
       <c r="M293" s="16"/>
       <c r="N293" s="17"/>
     </row>
-    <row r="294" spans="1:14">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A294" s="13"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
@@ -7539,7 +7545,7 @@
       <c r="M294" s="16"/>
       <c r="N294" s="17"/>
     </row>
-    <row r="295" spans="1:14">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A295" s="13"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
@@ -7561,7 +7567,7 @@
       <c r="M295" s="16"/>
       <c r="N295" s="17"/>
     </row>
-    <row r="296" spans="1:14">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A296" s="13"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
@@ -7583,7 +7589,7 @@
       <c r="M296" s="16"/>
       <c r="N296" s="17"/>
     </row>
-    <row r="297" spans="1:14">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A297" s="13"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
@@ -7605,7 +7611,7 @@
       <c r="M297" s="16"/>
       <c r="N297" s="17"/>
     </row>
-    <row r="298" spans="1:14">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A298" s="13"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
@@ -7627,7 +7633,7 @@
       <c r="M298" s="16"/>
       <c r="N298" s="17"/>
     </row>
-    <row r="299" spans="1:14">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A299" s="13"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
@@ -7649,7 +7655,7 @@
       <c r="M299" s="16"/>
       <c r="N299" s="17"/>
     </row>
-    <row r="300" spans="1:14">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A300" s="13"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
@@ -7671,7 +7677,7 @@
       <c r="M300" s="16"/>
       <c r="N300" s="17"/>
     </row>
-    <row r="301" spans="1:14">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A301" s="13"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
@@ -7693,7 +7699,7 @@
       <c r="M301" s="16"/>
       <c r="N301" s="17"/>
     </row>
-    <row r="302" spans="1:14">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A302" s="13"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
@@ -7715,7 +7721,7 @@
       <c r="M302" s="16"/>
       <c r="N302" s="17"/>
     </row>
-    <row r="303" spans="1:14">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A303" s="13"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
@@ -7737,7 +7743,7 @@
       <c r="M303" s="16"/>
       <c r="N303" s="17"/>
     </row>
-    <row r="304" spans="1:14">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A304" s="13"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
@@ -7759,7 +7765,7 @@
       <c r="M304" s="16"/>
       <c r="N304" s="17"/>
     </row>
-    <row r="305" spans="1:14">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A305" s="13"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
@@ -7781,7 +7787,7 @@
       <c r="M305" s="16"/>
       <c r="N305" s="17"/>
     </row>
-    <row r="306" spans="1:14">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A306" s="13"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
@@ -7803,7 +7809,7 @@
       <c r="M306" s="16"/>
       <c r="N306" s="17"/>
     </row>
-    <row r="307" spans="1:14">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A307" s="13"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
@@ -7825,7 +7831,7 @@
       <c r="M307" s="16"/>
       <c r="N307" s="17"/>
     </row>
-    <row r="308" spans="1:14">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A308" s="13"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
@@ -7847,7 +7853,7 @@
       <c r="M308" s="16"/>
       <c r="N308" s="17"/>
     </row>
-    <row r="309" spans="1:14">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A309" s="13"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
@@ -7869,7 +7875,7 @@
       <c r="M309" s="16"/>
       <c r="N309" s="17"/>
     </row>
-    <row r="310" spans="1:14">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A310" s="13"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
@@ -7891,7 +7897,7 @@
       <c r="M310" s="16"/>
       <c r="N310" s="17"/>
     </row>
-    <row r="311" spans="1:14">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A311" s="13"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
@@ -7913,7 +7919,7 @@
       <c r="M311" s="16"/>
       <c r="N311" s="17"/>
     </row>
-    <row r="312" spans="1:14">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A312" s="13"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
@@ -7935,7 +7941,7 @@
       <c r="M312" s="16"/>
       <c r="N312" s="17"/>
     </row>
-    <row r="313" spans="1:14">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A313" s="13"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
@@ -7957,7 +7963,7 @@
       <c r="M313" s="16"/>
       <c r="N313" s="17"/>
     </row>
-    <row r="314" spans="1:14">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A314" s="13"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
@@ -7979,7 +7985,7 @@
       <c r="M314" s="16"/>
       <c r="N314" s="17"/>
     </row>
-    <row r="315" spans="1:14">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A315" s="13"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
@@ -8001,7 +8007,7 @@
       <c r="M315" s="16"/>
       <c r="N315" s="17"/>
     </row>
-    <row r="316" spans="1:14">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A316" s="13"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
@@ -8023,7 +8029,7 @@
       <c r="M316" s="16"/>
       <c r="N316" s="17"/>
     </row>
-    <row r="317" spans="1:14">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A317" s="13"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
@@ -8045,7 +8051,7 @@
       <c r="M317" s="16"/>
       <c r="N317" s="17"/>
     </row>
-    <row r="318" spans="1:14">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A318" s="13"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
@@ -8067,7 +8073,7 @@
       <c r="M318" s="16"/>
       <c r="N318" s="17"/>
     </row>
-    <row r="319" spans="1:14">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A319" s="13"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
@@ -8089,7 +8095,7 @@
       <c r="M319" s="16"/>
       <c r="N319" s="17"/>
     </row>
-    <row r="320" spans="1:14">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A320" s="13"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
@@ -8111,7 +8117,7 @@
       <c r="M320" s="16"/>
       <c r="N320" s="17"/>
     </row>
-    <row r="321" spans="1:14">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A321" s="13"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
@@ -8133,7 +8139,7 @@
       <c r="M321" s="16"/>
       <c r="N321" s="17"/>
     </row>
-    <row r="322" spans="1:14">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A322" s="13"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
@@ -8155,7 +8161,7 @@
       <c r="M322" s="16"/>
       <c r="N322" s="17"/>
     </row>
-    <row r="323" spans="1:14">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A323" s="13"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
@@ -8177,7 +8183,7 @@
       <c r="M323" s="16"/>
       <c r="N323" s="17"/>
     </row>
-    <row r="324" spans="1:14">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A324" s="13"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
@@ -8199,7 +8205,7 @@
       <c r="M324" s="16"/>
       <c r="N324" s="17"/>
     </row>
-    <row r="325" spans="1:14">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A325" s="13"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
@@ -8221,7 +8227,7 @@
       <c r="M325" s="16"/>
       <c r="N325" s="17"/>
     </row>
-    <row r="326" spans="1:14">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A326" s="13"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
@@ -8243,7 +8249,7 @@
       <c r="M326" s="16"/>
       <c r="N326" s="17"/>
     </row>
-    <row r="327" spans="1:14">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A327" s="13"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
@@ -8265,7 +8271,7 @@
       <c r="M327" s="16"/>
       <c r="N327" s="17"/>
     </row>
-    <row r="328" spans="1:14">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A328" s="13"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
@@ -8287,7 +8293,7 @@
       <c r="M328" s="16"/>
       <c r="N328" s="17"/>
     </row>
-    <row r="329" spans="1:14">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A329" s="13"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
@@ -8309,7 +8315,7 @@
       <c r="M329" s="16"/>
       <c r="N329" s="17"/>
     </row>
-    <row r="330" spans="1:14">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A330" s="13"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
@@ -8331,7 +8337,7 @@
       <c r="M330" s="16"/>
       <c r="N330" s="17"/>
     </row>
-    <row r="331" spans="1:14">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A331" s="13"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
@@ -8353,7 +8359,7 @@
       <c r="M331" s="16"/>
       <c r="N331" s="17"/>
     </row>
-    <row r="332" spans="1:14">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A332" s="13"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
@@ -8375,7 +8381,7 @@
       <c r="M332" s="16"/>
       <c r="N332" s="17"/>
     </row>
-    <row r="333" spans="1:14">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A333" s="13"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
@@ -8397,7 +8403,7 @@
       <c r="M333" s="16"/>
       <c r="N333" s="17"/>
     </row>
-    <row r="334" spans="1:14">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A334" s="13"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
@@ -8419,7 +8425,7 @@
       <c r="M334" s="16"/>
       <c r="N334" s="17"/>
     </row>
-    <row r="335" spans="1:14">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A335" s="13"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
@@ -8441,7 +8447,7 @@
       <c r="M335" s="16"/>
       <c r="N335" s="17"/>
     </row>
-    <row r="336" spans="1:14">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A336" s="13"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
@@ -8463,7 +8469,7 @@
       <c r="M336" s="16"/>
       <c r="N336" s="17"/>
     </row>
-    <row r="337" spans="1:14">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A337" s="13"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
@@ -8485,7 +8491,7 @@
       <c r="M337" s="16"/>
       <c r="N337" s="17"/>
     </row>
-    <row r="338" spans="1:14">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A338" s="13"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
@@ -8507,7 +8513,7 @@
       <c r="M338" s="16"/>
       <c r="N338" s="17"/>
     </row>
-    <row r="339" spans="1:14">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A339" s="13"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
@@ -8529,7 +8535,7 @@
       <c r="M339" s="16"/>
       <c r="N339" s="17"/>
     </row>
-    <row r="340" spans="1:14">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A340" s="13"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
@@ -8551,7 +8557,7 @@
       <c r="M340" s="16"/>
       <c r="N340" s="17"/>
     </row>
-    <row r="341" spans="1:14">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A341" s="13"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
@@ -8573,7 +8579,7 @@
       <c r="M341" s="16"/>
       <c r="N341" s="17"/>
     </row>
-    <row r="342" spans="1:14">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A342" s="13"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
@@ -8595,7 +8601,7 @@
       <c r="M342" s="16"/>
       <c r="N342" s="17"/>
     </row>
-    <row r="343" spans="1:14">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A343" s="13"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
@@ -8617,7 +8623,7 @@
       <c r="M343" s="16"/>
       <c r="N343" s="17"/>
     </row>
-    <row r="344" spans="1:14">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A344" s="13"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
@@ -8639,7 +8645,7 @@
       <c r="M344" s="16"/>
       <c r="N344" s="17"/>
     </row>
-    <row r="345" spans="1:14">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A345" s="13"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
@@ -8661,7 +8667,7 @@
       <c r="M345" s="16"/>
       <c r="N345" s="17"/>
     </row>
-    <row r="346" spans="1:14">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A346" s="13"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
@@ -8683,7 +8689,7 @@
       <c r="M346" s="16"/>
       <c r="N346" s="17"/>
     </row>
-    <row r="347" spans="1:14">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A347" s="13"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
@@ -8705,7 +8711,7 @@
       <c r="M347" s="16"/>
       <c r="N347" s="17"/>
     </row>
-    <row r="348" spans="1:14">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A348" s="13"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
@@ -8727,7 +8733,7 @@
       <c r="M348" s="16"/>
       <c r="N348" s="17"/>
     </row>
-    <row r="349" spans="1:14">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A349" s="13"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
@@ -8749,7 +8755,7 @@
       <c r="M349" s="16"/>
       <c r="N349" s="17"/>
     </row>
-    <row r="350" spans="1:14">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A350" s="13"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
@@ -8771,7 +8777,7 @@
       <c r="M350" s="16"/>
       <c r="N350" s="17"/>
     </row>
-    <row r="351" spans="1:14">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A351" s="13"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
@@ -8793,7 +8799,7 @@
       <c r="M351" s="16"/>
       <c r="N351" s="17"/>
     </row>
-    <row r="352" spans="1:14">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A352" s="13"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
@@ -8815,7 +8821,7 @@
       <c r="M352" s="16"/>
       <c r="N352" s="17"/>
     </row>
-    <row r="353" spans="1:14">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A353" s="13"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
@@ -8837,7 +8843,7 @@
       <c r="M353" s="16"/>
       <c r="N353" s="17"/>
     </row>
-    <row r="354" spans="1:14">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A354" s="13"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
@@ -8859,7 +8865,7 @@
       <c r="M354" s="16"/>
       <c r="N354" s="17"/>
     </row>
-    <row r="355" spans="1:14">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A355" s="13"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
@@ -8881,7 +8887,7 @@
       <c r="M355" s="16"/>
       <c r="N355" s="17"/>
     </row>
-    <row r="356" spans="1:14">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A356" s="13"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
@@ -8903,7 +8909,7 @@
       <c r="M356" s="16"/>
       <c r="N356" s="17"/>
     </row>
-    <row r="357" spans="1:14">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A357" s="13"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
@@ -8925,7 +8931,7 @@
       <c r="M357" s="16"/>
       <c r="N357" s="17"/>
     </row>
-    <row r="358" spans="1:14">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A358" s="13"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
@@ -8947,7 +8953,7 @@
       <c r="M358" s="16"/>
       <c r="N358" s="17"/>
     </row>
-    <row r="359" spans="1:14">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A359" s="13"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
@@ -8969,7 +8975,7 @@
       <c r="M359" s="16"/>
       <c r="N359" s="17"/>
     </row>
-    <row r="360" spans="1:14">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A360" s="13"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
@@ -8991,7 +8997,7 @@
       <c r="M360" s="16"/>
       <c r="N360" s="17"/>
     </row>
-    <row r="361" spans="1:14">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A361" s="13"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
@@ -9013,7 +9019,7 @@
       <c r="M361" s="16"/>
       <c r="N361" s="17"/>
     </row>
-    <row r="362" spans="1:14">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A362" s="13"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
@@ -9035,7 +9041,7 @@
       <c r="M362" s="16"/>
       <c r="N362" s="17"/>
     </row>
-    <row r="363" spans="1:14">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A363" s="13"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
@@ -9057,7 +9063,7 @@
       <c r="M363" s="16"/>
       <c r="N363" s="17"/>
     </row>
-    <row r="364" spans="1:14">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A364" s="13"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
@@ -9079,7 +9085,7 @@
       <c r="M364" s="16"/>
       <c r="N364" s="17"/>
     </row>
-    <row r="365" spans="1:14">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A365" s="13"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
@@ -9101,7 +9107,7 @@
       <c r="M365" s="16"/>
       <c r="N365" s="17"/>
     </row>
-    <row r="366" spans="1:14">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A366" s="13"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
@@ -9123,7 +9129,7 @@
       <c r="M366" s="16"/>
       <c r="N366" s="17"/>
     </row>
-    <row r="367" spans="1:14">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A367" s="13"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
@@ -9145,7 +9151,7 @@
       <c r="M367" s="16"/>
       <c r="N367" s="17"/>
     </row>
-    <row r="368" spans="1:14">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A368" s="13"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
@@ -9167,7 +9173,7 @@
       <c r="M368" s="16"/>
       <c r="N368" s="17"/>
     </row>
-    <row r="369" spans="1:14">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A369" s="13"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
@@ -9189,7 +9195,7 @@
       <c r="M369" s="16"/>
       <c r="N369" s="17"/>
     </row>
-    <row r="370" spans="1:14">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A370" s="13"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
@@ -9211,7 +9217,7 @@
       <c r="M370" s="16"/>
       <c r="N370" s="17"/>
     </row>
-    <row r="371" spans="1:14">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A371" s="13"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
@@ -9233,7 +9239,7 @@
       <c r="M371" s="16"/>
       <c r="N371" s="17"/>
     </row>
-    <row r="372" spans="1:14">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A372" s="13"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
@@ -9255,7 +9261,7 @@
       <c r="M372" s="16"/>
       <c r="N372" s="17"/>
     </row>
-    <row r="373" spans="1:14">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A373" s="13"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
@@ -9277,7 +9283,7 @@
       <c r="M373" s="16"/>
       <c r="N373" s="17"/>
     </row>
-    <row r="374" spans="1:14">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A374" s="13"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
@@ -9299,7 +9305,7 @@
       <c r="M374" s="16"/>
       <c r="N374" s="17"/>
     </row>
-    <row r="375" spans="1:14">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A375" s="13"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
@@ -9321,7 +9327,7 @@
       <c r="M375" s="16"/>
       <c r="N375" s="17"/>
     </row>
-    <row r="376" spans="1:14">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A376" s="13"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
@@ -9343,7 +9349,7 @@
       <c r="M376" s="16"/>
       <c r="N376" s="17"/>
     </row>
-    <row r="377" spans="1:14">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A377" s="13"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
@@ -9365,7 +9371,7 @@
       <c r="M377" s="16"/>
       <c r="N377" s="17"/>
     </row>
-    <row r="378" spans="1:14">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A378" s="13"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
@@ -9387,7 +9393,7 @@
       <c r="M378" s="16"/>
       <c r="N378" s="17"/>
     </row>
-    <row r="379" spans="1:14">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A379" s="13"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
@@ -9409,7 +9415,7 @@
       <c r="M379" s="16"/>
       <c r="N379" s="17"/>
     </row>
-    <row r="380" spans="1:14">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A380" s="13"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
@@ -9431,7 +9437,7 @@
       <c r="M380" s="16"/>
       <c r="N380" s="17"/>
     </row>
-    <row r="381" spans="1:14">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A381" s="13"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
@@ -9453,7 +9459,7 @@
       <c r="M381" s="16"/>
       <c r="N381" s="17"/>
     </row>
-    <row r="382" spans="1:14">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A382" s="13"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
@@ -9475,7 +9481,7 @@
       <c r="M382" s="16"/>
       <c r="N382" s="17"/>
     </row>
-    <row r="383" spans="1:14">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A383" s="13"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
@@ -9497,7 +9503,7 @@
       <c r="M383" s="16"/>
       <c r="N383" s="17"/>
     </row>
-    <row r="384" spans="1:14">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A384" s="13"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -9519,7 +9525,7 @@
       <c r="M384" s="16"/>
       <c r="N384" s="17"/>
     </row>
-    <row r="385" spans="1:14">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A385" s="13"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
@@ -9541,7 +9547,7 @@
       <c r="M385" s="16"/>
       <c r="N385" s="17"/>
     </row>
-    <row r="386" spans="1:14">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A386" s="13"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -9563,7 +9569,7 @@
       <c r="M386" s="16"/>
       <c r="N386" s="17"/>
     </row>
-    <row r="387" spans="1:14">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A387" s="13"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -9585,7 +9591,7 @@
       <c r="M387" s="16"/>
       <c r="N387" s="17"/>
     </row>
-    <row r="388" spans="1:14">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A388" s="13"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -9607,7 +9613,7 @@
       <c r="M388" s="16"/>
       <c r="N388" s="17"/>
     </row>
-    <row r="389" spans="1:14">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A389" s="13"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
@@ -9629,7 +9635,7 @@
       <c r="M389" s="16"/>
       <c r="N389" s="17"/>
     </row>
-    <row r="390" spans="1:14">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A390" s="13"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
@@ -9651,7 +9657,7 @@
       <c r="M390" s="16"/>
       <c r="N390" s="17"/>
     </row>
-    <row r="391" spans="1:14">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A391" s="13"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
@@ -9673,7 +9679,7 @@
       <c r="M391" s="16"/>
       <c r="N391" s="17"/>
     </row>
-    <row r="392" spans="1:14">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A392" s="13"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -9695,7 +9701,7 @@
       <c r="M392" s="16"/>
       <c r="N392" s="17"/>
     </row>
-    <row r="393" spans="1:14">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A393" s="13"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
@@ -9717,7 +9723,7 @@
       <c r="M393" s="16"/>
       <c r="N393" s="17"/>
     </row>
-    <row r="394" spans="1:14">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A394" s="13"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -9739,7 +9745,7 @@
       <c r="M394" s="16"/>
       <c r="N394" s="17"/>
     </row>
-    <row r="395" spans="1:14">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A395" s="13"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -9761,7 +9767,7 @@
       <c r="M395" s="16"/>
       <c r="N395" s="17"/>
     </row>
-    <row r="396" spans="1:14">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A396" s="13"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
@@ -9783,7 +9789,7 @@
       <c r="M396" s="16"/>
       <c r="N396" s="17"/>
     </row>
-    <row r="397" spans="1:14">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A397" s="13"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
@@ -9805,7 +9811,7 @@
       <c r="M397" s="16"/>
       <c r="N397" s="17"/>
     </row>
-    <row r="398" spans="1:14">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A398" s="13"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -9827,7 +9833,7 @@
       <c r="M398" s="16"/>
       <c r="N398" s="17"/>
     </row>
-    <row r="399" spans="1:14">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A399" s="13"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
@@ -9849,7 +9855,7 @@
       <c r="M399" s="16"/>
       <c r="N399" s="17"/>
     </row>
-    <row r="400" spans="1:14">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A400" s="13"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -9871,7 +9877,7 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A401" s="13"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>

--- a/1234567.xlxs.xlsx
+++ b/1234567.xlxs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sachi\Desktop\CAP776\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F9E416-0873-47EB-B7A8-F07D1797E622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC72720-9891-441F-89EA-F132C78886E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,60 @@
   </si>
   <si>
     <t>Mood is good feeling homesick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felt tired and sat in room after classes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felt good and had chit chat with friends </t>
+  </si>
+  <si>
+    <t>Was excited and joyed on visiting my hometown for rakhi festival.</t>
+  </si>
+  <si>
+    <t>Happy celebrated festival with my family .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spent time with my family </t>
+  </si>
+  <si>
+    <t xml:space="preserve">did my studies and spent the evening with my brother </t>
+  </si>
+  <si>
+    <t>back to hostel missed my classes but did my revision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">had s nice day was back from home and attended all my classes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">it was a nice but tireful day </t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it was a very tiry day and I slipped in college </t>
+  </si>
+  <si>
+    <t>came back home from college as my condition was getting worse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">got myself diagonsed and came to know my tailbone got dislocated and now I am on bedrest </t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>missing college and friends as I am still on bedrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feeling tired and dizzy </t>
+  </si>
+  <si>
+    <t>feeling tired and bored</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1389,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="13">
         <v>46259</v>
       </c>
@@ -1345,331 +1399,685 @@
       <c r="C13" s="14">
         <v>50</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
+      <c r="D13" s="14">
+        <v>60</v>
+      </c>
+      <c r="E13" s="14">
+        <v>40</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>120</v>
+      </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>450</v>
+        <v>1020</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>990</v>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+        <v>420</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B14" s="14">
+        <v>500</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>60</v>
+      </c>
+      <c r="E14" s="14">
+        <v>40</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>210</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+        <v>400</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B15" s="14">
+        <v>350</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>60</v>
+      </c>
+      <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>180</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+        <v>350</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B16" s="14">
+        <v>600</v>
+      </c>
+      <c r="C16" s="14">
+        <v>10</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>30</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>300</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B17" s="14">
+        <v>550</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>80</v>
+      </c>
+      <c r="E17" s="14">
+        <v>40</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>200</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+        <v>510</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B18" s="14">
+        <v>600</v>
+      </c>
+      <c r="C18" s="14">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14">
+        <v>70</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>150</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+        <v>500</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B19" s="14">
+        <v>400</v>
+      </c>
+      <c r="C19" s="14">
+        <v>40</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>120</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>300</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+        <v>460</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B20" s="14">
+        <v>400</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
+        <v>60</v>
+      </c>
+      <c r="E20" s="14">
+        <v>40</v>
+      </c>
+      <c r="F20" s="14">
+        <v>400</v>
+      </c>
+      <c r="G20" s="14">
+        <v>8</v>
+      </c>
+      <c r="H20" s="14">
+        <v>100</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B21" s="14">
+        <v>500</v>
+      </c>
+      <c r="C21" s="14">
+        <v>55</v>
+      </c>
+      <c r="D21" s="14">
+        <v>150</v>
+      </c>
+      <c r="E21" s="14">
+        <v>50</v>
+      </c>
+      <c r="F21" s="14">
+        <v>200</v>
+      </c>
+      <c r="G21" s="14">
+        <v>4</v>
+      </c>
+      <c r="H21" s="14">
+        <v>100</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1055</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+        <v>385</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B22" s="14">
+        <v>300</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>40</v>
+      </c>
+      <c r="E22" s="14">
+        <v>20</v>
+      </c>
+      <c r="F22" s="14">
+        <v>350</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
+        <v>200</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+        <v>470</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B23" s="14">
+        <v>450</v>
+      </c>
+      <c r="C23" s="14">
+        <v>40</v>
+      </c>
+      <c r="D23" s="14">
+        <v>40</v>
+      </c>
+      <c r="E23" s="14">
+        <v>30</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>300</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+        <v>280</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A24" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B24" s="14">
+        <v>300</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>20</v>
+      </c>
+      <c r="E24" s="14">
+        <v>10</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>200</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B25" s="14">
+        <v>600</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>50</v>
+      </c>
+      <c r="E25" s="14">
+        <v>20</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>100</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>670</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B26" s="14">
+        <v>600</v>
+      </c>
+      <c r="C26" s="14">
+        <v>10</v>
+      </c>
+      <c r="D26" s="14">
+        <v>40</v>
+      </c>
+      <c r="E26" s="14">
+        <v>20</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>300</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B27" s="14">
+        <v>600</v>
+      </c>
+      <c r="C27" s="14">
+        <v>10</v>
+      </c>
+      <c r="D27" s="14">
+        <v>50</v>
+      </c>
+      <c r="E27" s="14">
+        <v>20</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>400</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>
@@ -9909,7 +10317,7 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/1234567.xlxs.xlsx
+++ b/1234567.xlxs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sachi\Desktop\CAP776\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC72720-9891-441F-89EA-F132C78886E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95955F34-387E-4038-974F-5A6050BD7901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,12 @@
   </si>
   <si>
     <t>feeling tired and bored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feeling better and healing </t>
+  </si>
+  <si>
+    <t>feeling uneasy from taking too many medicines</t>
   </si>
 </sst>
 </file>
@@ -2080,48 +2086,96 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B28" s="14">
+        <v>700</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>40</v>
+      </c>
+      <c r="E28" s="14">
+        <v>20</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>400</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>250</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B29" s="14">
+        <v>840</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>40</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>300</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>

--- a/1234567.xlxs.xlsx
+++ b/1234567.xlxs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sachi\Desktop\CAP776\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95955F34-387E-4038-974F-5A6050BD7901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F265F46A-8930-4BD2-B39D-7531D5A89D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,24 @@
   </si>
   <si>
     <t>feeling uneasy from taking too many medicines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feeling low and not satisfied </t>
+  </si>
+  <si>
+    <t xml:space="preserve">feeling okay </t>
+  </si>
+  <si>
+    <t xml:space="preserve">feeling a bit tired sitting at home </t>
+  </si>
+  <si>
+    <t>got sick few days back and got hospitalized</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feeling okayish today and missing my friends </t>
+  </si>
+  <si>
+    <t>feeling better today and looked after my syllabus</t>
   </si>
 </sst>
 </file>
@@ -2178,158 +2196,326 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B30" s="14">
+        <v>840</v>
+      </c>
+      <c r="C30" s="14">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
+        <v>20</v>
+      </c>
+      <c r="E30" s="14">
+        <v>20</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>300</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B31" s="14">
+        <v>800</v>
+      </c>
+      <c r="C31" s="14">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
+        <v>30</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>400</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B32" s="14">
+        <v>600</v>
+      </c>
+      <c r="C32" s="14">
+        <v>25</v>
+      </c>
+      <c r="D32" s="14">
+        <v>20</v>
+      </c>
+      <c r="E32" s="14">
+        <v>30</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>400</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+        <v>365</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A33" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B33" s="14">
+        <v>680</v>
+      </c>
+      <c r="C33" s="14">
+        <v>10</v>
+      </c>
+      <c r="D33" s="14">
+        <v>40</v>
+      </c>
+      <c r="E33" s="14">
+        <v>30</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>300</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>380</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A34" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B34" s="14">
+        <v>800</v>
+      </c>
+      <c r="C34" s="14">
+        <v>10</v>
+      </c>
+      <c r="D34" s="14">
+        <v>10</v>
+      </c>
+      <c r="E34" s="14">
+        <v>30</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>500</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="14">
+        <v>700</v>
+      </c>
+      <c r="C35" s="14">
+        <v>20</v>
+      </c>
+      <c r="D35" s="14">
+        <v>50</v>
+      </c>
+      <c r="E35" s="14">
+        <v>20</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>500</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+        <v>150</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B36" s="14">
+        <v>750</v>
+      </c>
+      <c r="C36" s="14">
+        <v>30</v>
+      </c>
+      <c r="D36" s="14">
+        <v>30</v>
+      </c>
+      <c r="E36" s="14">
+        <v>20</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>450</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13"/>

--- a/1234567.xlxs.xlsx
+++ b/1234567.xlxs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sachi\Desktop\CAP776\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F265F46A-8930-4BD2-B39D-7531D5A89D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761BD146-14D9-4DBE-B70C-9FCB422617E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t>feeling better today and looked after my syllabus</t>
+  </si>
+  <si>
+    <t>feeling better</t>
   </si>
 </sst>
 </file>
@@ -2518,26 +2521,50 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B37" s="14">
+        <v>700</v>
+      </c>
+      <c r="C37" s="14">
+        <v>30</v>
+      </c>
+      <c r="D37" s="14">
+        <v>45</v>
+      </c>
+      <c r="E37" s="14">
+        <v>30</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>500</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1305</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>135</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13"/>

--- a/1234567.xlxs.xlsx
+++ b/1234567.xlxs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sachi\Desktop\CAP776\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761BD146-14D9-4DBE-B70C-9FCB422617E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9988DD-6F5E-4915-B4E3-67B868BA1DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t>feeling better</t>
+  </si>
+  <si>
+    <t>revised my syllabus</t>
   </si>
 </sst>
 </file>
@@ -2567,26 +2570,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B38" s="14">
+        <v>600</v>
+      </c>
+      <c r="C38" s="14">
+        <v>20</v>
+      </c>
+      <c r="D38" s="14">
+        <v>60</v>
+      </c>
+      <c r="E38" s="14">
+        <v>20</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>400</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13"/>

--- a/1234567.xlxs.xlsx
+++ b/1234567.xlxs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sachi\Desktop\CAP776\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9988DD-6F5E-4915-B4E3-67B868BA1DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F83246-21F0-4615-B8AA-F8318296DDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -319,6 +319,12 @@
   </si>
   <si>
     <t>revised my syllabus</t>
+  </si>
+  <si>
+    <t>feeling a bit tired and homesick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revised my syllabus for upcoming ca </t>
   </si>
 </sst>
 </file>
@@ -969,7 +975,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N402"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1099,36 +1105,36 @@
     </row>
     <row r="6" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B6" s="9">
+        <v>400</v>
+      </c>
+      <c r="C6" s="9">
+        <v>40</v>
+      </c>
+      <c r="D6" s="9">
+        <v>40</v>
+      </c>
+      <c r="E6" s="9">
+        <v>30</v>
+      </c>
+      <c r="F6" s="9">
         <v>300</v>
       </c>
-      <c r="C6" s="9">
-        <v>10</v>
-      </c>
-      <c r="D6" s="9">
-        <v>50</v>
-      </c>
-      <c r="E6" s="9">
-        <v>20</v>
-      </c>
-      <c r="F6" s="9">
+      <c r="G6" s="9">
+        <v>6</v>
+      </c>
+      <c r="H6" s="9">
         <v>400</v>
       </c>
-      <c r="G6" s="9">
-        <v>8</v>
-      </c>
-      <c r="H6" s="9">
-        <v>20</v>
-      </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>800</v>
+        <f t="shared" ref="I6:I70" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <v>1210</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
-        <v>640</v>
+        <f t="shared" ref="J6:J70" si="1">IF(I6="","",1440-I6)</f>
+        <v>230</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>53</v>
@@ -1143,205 +1149,203 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="13">
+    <row r="7" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B7" s="9">
+        <v>400</v>
+      </c>
+      <c r="C7" s="9">
+        <v>20</v>
+      </c>
+      <c r="D7" s="9">
+        <v>120</v>
+      </c>
+      <c r="E7" s="9">
+        <v>90</v>
+      </c>
+      <c r="F7" s="9">
+        <v>200</v>
+      </c>
+      <c r="G7" s="9">
+        <v>4</v>
+      </c>
+      <c r="H7" s="9">
+        <v>20</v>
+      </c>
+      <c r="I7" s="10">
+        <v>850</v>
+      </c>
+      <c r="J7" s="10">
+        <v>590</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="13">
         <v>46253</v>
-      </c>
-      <c r="B7" s="14">
-        <v>350</v>
-      </c>
-      <c r="C7" s="14">
-        <v>15</v>
-      </c>
-      <c r="D7" s="14">
-        <v>60</v>
-      </c>
-      <c r="E7" s="14">
-        <v>20</v>
-      </c>
-      <c r="F7" s="14">
-        <v>200</v>
-      </c>
-      <c r="G7" s="14">
-        <v>4</v>
-      </c>
-      <c r="H7" s="14">
-        <v>30</v>
-      </c>
-      <c r="I7" s="15">
-        <f t="shared" si="0"/>
-        <v>675</v>
-      </c>
-      <c r="J7" s="15">
-        <f t="shared" si="1"/>
-        <v>765</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="13">
-        <v>46254</v>
       </c>
       <c r="B8" s="14">
         <v>350</v>
       </c>
       <c r="C8" s="14">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D8" s="14">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E8" s="14">
         <v>20</v>
       </c>
       <c r="F8" s="14">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G8" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H8" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>820</v>
+        <v>705</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>735</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>56</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>54</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="13">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B9" s="14">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="C9" s="14">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D9" s="14">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E9" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G9" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" s="14">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>910</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>530</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>56</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M9" s="16" t="s">
         <v>54</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="B10" s="14">
-        <v>720</v>
+        <v>400</v>
       </c>
       <c r="C10" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D10" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E10" s="14">
         <v>30</v>
       </c>
       <c r="F10" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G10" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H10" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="B11" s="14">
-        <v>400</v>
+        <v>720</v>
       </c>
       <c r="C11" s="14">
         <v>20</v>
       </c>
       <c r="D11" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E11" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F11" s="14">
         <v>0</v>
@@ -1350,24 +1354,24 @@
         <v>0</v>
       </c>
       <c r="H11" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>565</v>
+        <v>870</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>875</v>
+        <v>570</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>53</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="N11" s="17" t="s">
         <v>63</v>
@@ -1375,82 +1379,82 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="B12" s="14">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C12" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D12" s="14">
+        <v>50</v>
+      </c>
+      <c r="E12" s="14">
+        <v>35</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
         <v>60</v>
-      </c>
-      <c r="E12" s="14">
-        <v>30</v>
-      </c>
-      <c r="F12" s="14">
-        <v>150</v>
-      </c>
-      <c r="G12" s="14">
-        <v>3</v>
-      </c>
-      <c r="H12" s="14">
-        <v>20</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>650</v>
+        <v>565</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>790</v>
+        <v>875</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>56</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>54</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B13" s="14">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="C13" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D13" s="14">
         <v>60</v>
       </c>
       <c r="E13" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F13" s="14">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="G13" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H13" s="14">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>650</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>790</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>56</v>
@@ -1462,18 +1466,18 @@
         <v>54</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="13">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B14" s="14">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C14" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D14" s="14">
         <v>60</v>
@@ -1482,21 +1486,21 @@
         <v>40</v>
       </c>
       <c r="F14" s="14">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G14" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H14" s="14">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>56</v>
@@ -1508,116 +1512,116 @@
         <v>54</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="13">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B15" s="14">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="C15" s="14">
         <v>30</v>
       </c>
       <c r="D15" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E15" s="14">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F15" s="14">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G15" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1040</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>56</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>54</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="13">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B16" s="14">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="C16" s="14">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D16" s="14">
         <v>120</v>
       </c>
       <c r="E16" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F16" s="14">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G16" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>1090</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>56</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>54</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="13">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B17" s="14">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="C17" s="14">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E17" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F17" s="14">
         <v>0</v>
@@ -1626,15 +1630,15 @@
         <v>0</v>
       </c>
       <c r="H17" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>1060</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>380</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>56</v>
@@ -1646,24 +1650,24 @@
         <v>54</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B18" s="14">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="C18" s="14">
         <v>60</v>
       </c>
       <c r="D18" s="14">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E18" s="14">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F18" s="14">
         <v>0</v>
@@ -1672,15 +1676,15 @@
         <v>0</v>
       </c>
       <c r="H18" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>940</v>
+        <v>930</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>56</v>
@@ -1692,24 +1696,24 @@
         <v>54</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="13">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B19" s="14">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C19" s="14">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D19" s="14">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="E19" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F19" s="14">
         <v>0</v>
@@ -1718,15 +1722,15 @@
         <v>0</v>
       </c>
       <c r="H19" s="14">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>980</v>
+        <v>940</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>56</v>
@@ -1738,225 +1742,225 @@
         <v>54</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="13">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B20" s="14">
         <v>400</v>
       </c>
       <c r="C20" s="14">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D20" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E20" s="14">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="F20" s="14">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H20" s="14">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>980</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>460</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>56</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M20" s="16" t="s">
         <v>54</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="13">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B21" s="14">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C21" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D21" s="14">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="E21" s="14">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F21" s="14">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G21" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H21" s="14">
         <v>100</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>56</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M21" s="16" t="s">
         <v>54</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B22" s="14">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="C22" s="14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D22" s="14">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="E22" s="14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F22" s="14">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>970</v>
+        <v>1055</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>385</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="L22" s="16" t="s">
         <v>57</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="13">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B23" s="14">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="C23" s="14">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D23" s="14">
         <v>40</v>
       </c>
       <c r="E23" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F23" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>1160</v>
+        <v>970</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>470</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M23" s="16" t="s">
         <v>75</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="13">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B24" s="14">
+        <v>450</v>
+      </c>
+      <c r="C24" s="14">
+        <v>40</v>
+      </c>
+      <c r="D24" s="14">
+        <v>40</v>
+      </c>
+      <c r="E24" s="14">
+        <v>30</v>
+      </c>
+      <c r="F24" s="14">
         <v>300</v>
       </c>
-      <c r="C24" s="14">
-        <v>0</v>
-      </c>
-      <c r="D24" s="14">
-        <v>20</v>
-      </c>
-      <c r="E24" s="14">
-        <v>10</v>
-      </c>
-      <c r="F24" s="14">
-        <v>0</v>
-      </c>
       <c r="G24" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H24" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>530</v>
+        <v>1160</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>910</v>
+        <v>280</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>75</v>
@@ -1968,24 +1972,24 @@
         <v>75</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A25" s="13">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B25" s="14">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="C25" s="14">
         <v>0</v>
       </c>
       <c r="D25" s="14">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E25" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F25" s="14">
         <v>0</v>
@@ -1994,41 +1998,41 @@
         <v>0</v>
       </c>
       <c r="H25" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>770</v>
+        <v>530</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>670</v>
+        <v>910</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>75</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="13">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B26" s="14">
         <v>600</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D26" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E26" s="14">
         <v>20</v>
@@ -2040,32 +2044,32 @@
         <v>0</v>
       </c>
       <c r="H26" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>970</v>
+        <v>770</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>670</v>
       </c>
       <c r="K26" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M26" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="L26" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>54</v>
-      </c>
       <c r="N26" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B27" s="14">
         <v>600</v>
@@ -2074,7 +2078,7 @@
         <v>10</v>
       </c>
       <c r="D27" s="14">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E27" s="14">
         <v>20</v>
@@ -2086,15 +2090,15 @@
         <v>0</v>
       </c>
       <c r="H27" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>970</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>470</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>75</v>
@@ -2103,24 +2107,24 @@
         <v>53</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B28" s="14">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="C28" s="14">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D28" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E28" s="14">
         <v>20</v>
@@ -2136,14 +2140,14 @@
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>1190</v>
+        <v>1080</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="L28" s="16" t="s">
         <v>53</v>
@@ -2152,15 +2156,15 @@
         <v>75</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B29" s="14">
-        <v>840</v>
+        <v>700</v>
       </c>
       <c r="C29" s="14">
         <v>30</v>
@@ -2169,7 +2173,7 @@
         <v>40</v>
       </c>
       <c r="E29" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F29" s="14">
         <v>0</v>
@@ -2178,44 +2182,44 @@
         <v>0</v>
       </c>
       <c r="H29" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>1240</v>
+        <v>1190</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="L29" s="16" t="s">
         <v>53</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B30" s="14">
         <v>840</v>
       </c>
       <c r="C30" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D30" s="14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E30" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F30" s="14">
         <v>0</v>
@@ -2228,11 +2232,11 @@
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1240</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="K30" s="16" t="s">
         <v>75</v>
@@ -2244,24 +2248,24 @@
         <v>54</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B31" s="14">
-        <v>800</v>
+        <v>840</v>
       </c>
       <c r="C31" s="14">
         <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E31" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F31" s="14">
         <v>0</v>
@@ -2270,15 +2274,15 @@
         <v>0</v>
       </c>
       <c r="H31" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>1280</v>
+        <v>1200</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>75</v>
@@ -2290,21 +2294,21 @@
         <v>54</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B32" s="14">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="C32" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D32" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E32" s="14">
         <v>30</v>
@@ -2320,11 +2324,11 @@
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>1075</v>
+        <v>1280</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>365</v>
+        <v>160</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>75</v>
@@ -2333,24 +2337,24 @@
         <v>53</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B33" s="14">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="C33" s="14">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D33" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E33" s="14">
         <v>30</v>
@@ -2362,15 +2366,15 @@
         <v>0</v>
       </c>
       <c r="H33" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>1075</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>75</v>
@@ -2382,21 +2386,21 @@
         <v>75</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="13">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B34" s="14">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="C34" s="14">
         <v>10</v>
       </c>
       <c r="D34" s="14">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E34" s="14">
         <v>30</v>
@@ -2408,15 +2412,15 @@
         <v>0</v>
       </c>
       <c r="H34" s="14">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>1350</v>
+        <v>1060</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>380</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>75</v>
@@ -2428,24 +2432,24 @@
         <v>75</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="13">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B35" s="14">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="C35" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D35" s="14">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E35" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F35" s="14">
         <v>0</v>
@@ -2458,11 +2462,11 @@
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>1290</v>
+        <v>1350</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>75</v>
@@ -2471,24 +2475,24 @@
         <v>53</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B36" s="14">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="C36" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D36" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E36" s="14">
         <v>20</v>
@@ -2500,18 +2504,18 @@
         <v>0</v>
       </c>
       <c r="H36" s="14">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v>1280</v>
+        <v>1290</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="L36" s="16" t="s">
         <v>53</v>
@@ -2520,24 +2524,24 @@
         <v>54</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="13">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B37" s="14">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="C37" s="14">
         <v>30</v>
       </c>
       <c r="D37" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E37" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F37" s="14">
         <v>0</v>
@@ -2546,44 +2550,44 @@
         <v>0</v>
       </c>
       <c r="H37" s="14">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>1305</v>
+        <v>1280</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>56</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M37" s="16" t="s">
         <v>54</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B38" s="14">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="C38" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D38" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E38" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F38" s="14">
         <v>0</v>
@@ -2592,15 +2596,15 @@
         <v>0</v>
       </c>
       <c r="H38" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>1100</v>
+        <v>1305</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>56</v>
@@ -2612,52 +2616,100 @@
         <v>54</v>
       </c>
       <c r="N38" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A39" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="14">
+        <v>600</v>
+      </c>
+      <c r="C39" s="14">
+        <v>20</v>
+      </c>
+      <c r="D39" s="14">
+        <v>60</v>
+      </c>
+      <c r="E39" s="14">
+        <v>20</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>400</v>
+      </c>
+      <c r="I39" s="15">
+        <f t="shared" si="0"/>
+        <v>1100</v>
+      </c>
+      <c r="J39" s="15">
+        <f t="shared" si="1"/>
+        <v>340</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N39" s="17" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+    <row r="40" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="14">
+        <v>300</v>
+      </c>
+      <c r="C40" s="14">
+        <v>60</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>40</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>200</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="13"/>
@@ -3307,11 +3359,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3329,11 +3381,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I71:I134" si="2">IF(SUM(B71:F71,H71)=0,"",SUM(B71:F71,H71))</f>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J71:J134" si="3">IF(I71="","",1440-I71)</f>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -4715,11 +4767,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4737,11 +4789,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I135:I198" si="4">IF(SUM(B135:F135,H135)=0,"",SUM(B135:F135,H135))</f>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J135:J198" si="5">IF(I135="","",1440-I135)</f>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -6123,11 +6175,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6145,11 +6197,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I199:I262" si="6">IF(SUM(B199:F199,H199)=0,"",SUM(B199:F199,H199))</f>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J199:J262" si="7">IF(I199="","",1440-I199)</f>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -7531,11 +7583,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7553,11 +7605,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I263:I326" si="8">IF(SUM(B263:F263,H263)=0,"",SUM(B263:F263,H263))</f>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J263:J326" si="9">IF(I263="","",1440-I263)</f>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -8939,11 +8991,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8961,11 +9013,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I327:I390" si="10">IF(SUM(B327:F327,H327)=0,"",SUM(B327:F327,H327))</f>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J327:J390" si="11">IF(I327="","",1440-I327)</f>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -10347,11 +10399,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10369,11 +10421,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I391:I402" si="12">IF(SUM(B391:F391,H391)=0,"",SUM(B391:F391,H391))</f>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J391:J402" si="13">IF(I391="","",1440-I391)</f>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10601,6 +10653,28 @@
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
     </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10610,21 +10684,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J402">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K402" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L402" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M402" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
